--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Liquid Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Liquid Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="292">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Liquid Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,856 +64,712 @@
     <t>Government Securities</t>
   </si>
   <si>
-    <t>State Government of Assam</t>
-  </si>
-  <si>
-    <t>IN1220140033</t>
+    <t>State Government of Gujarat</t>
+  </si>
+  <si>
+    <t>IN1520150039</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>State Government of Maharashtra</t>
-  </si>
-  <si>
-    <t>IN2220140213</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E08LO4</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
+    <t>Bajaj Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE377Y07334</t>
+  </si>
+  <si>
     <t>LIC Housing Finance Ltd. **</t>
   </si>
   <si>
-    <t>INE115A07PQ9</t>
-  </si>
-  <si>
-    <t>CRISIL AAA</t>
-  </si>
-  <si>
-    <t>TMF Holdings Ltd. **</t>
-  </si>
-  <si>
-    <t>INE909H08444</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
+    <t>INE115A07PU1</t>
+  </si>
+  <si>
+    <t>Zero Coupon Bonds / Deep Discount Bonds</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>Privately Placed/unlisted</t>
+  </si>
+  <si>
+    <t>Securitized Debt Instruments</t>
+  </si>
+  <si>
+    <t>Term Deposits</t>
+  </si>
+  <si>
+    <t>Deposits (maturity not exceeding 91 days)</t>
+  </si>
+  <si>
+    <t>Deposits (Placed as Margin)</t>
+  </si>
+  <si>
+    <t>Money Market Instruments</t>
+  </si>
+  <si>
+    <t>Certificate of Deposits</t>
+  </si>
+  <si>
+    <t>Punjab National Bank</t>
+  </si>
+  <si>
+    <t>INE160A16RL3</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
+  </si>
+  <si>
+    <t>Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE084A16DQ4</t>
+  </si>
+  <si>
+    <t>Punjab National Bank **</t>
+  </si>
+  <si>
+    <t>INE160A16RV2</t>
+  </si>
+  <si>
+    <t>Indian Bank **</t>
+  </si>
+  <si>
+    <t>INE562A16NH7</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda **</t>
+  </si>
+  <si>
+    <t>INE028A16IQ0</t>
+  </si>
+  <si>
+    <t>FITCH A1+</t>
+  </si>
+  <si>
+    <t>RBL Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE976G16OA9</t>
+  </si>
+  <si>
+    <t>ICRA A1+</t>
+  </si>
+  <si>
+    <t>Canara Bank **</t>
+  </si>
+  <si>
+    <t>INE476A16C06</t>
+  </si>
+  <si>
+    <t>INE084A16DH3</t>
   </si>
   <si>
     <t>HDFC Bank Ltd.</t>
   </si>
   <si>
-    <t>INE040A08948</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Financial Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE774D07UI4</t>
-  </si>
-  <si>
-    <t>FITCH AAA</t>
-  </si>
-  <si>
-    <t>Can Fin Homes Ltd. **</t>
-  </si>
-  <si>
-    <t>INE477A07316</t>
-  </si>
-  <si>
-    <t>ICRA AAA</t>
-  </si>
-  <si>
-    <t>John Deere Financial India Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE00V208074</t>
-  </si>
-  <si>
-    <t>Cholamandalam Investment And Finance Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE121A07RB5</t>
-  </si>
-  <si>
-    <t>ICRA AA+</t>
-  </si>
-  <si>
-    <t>INE121A07QI2</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd. **</t>
-  </si>
-  <si>
-    <t>INE081A08231</t>
-  </si>
-  <si>
-    <t>FITCH AA+</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE018E08193</t>
-  </si>
-  <si>
-    <t>Zero Coupon Bonds / Deep Discount Bonds</t>
-  </si>
-  <si>
-    <t>Nil</t>
-  </si>
-  <si>
-    <t>Privately Placed/unlisted</t>
-  </si>
-  <si>
-    <t>Securitized Debt Instruments</t>
-  </si>
-  <si>
-    <t>Term Deposits</t>
-  </si>
-  <si>
-    <t>Deposits (maturity not exceeding 91 days)</t>
-  </si>
-  <si>
-    <t>Deposits (Placed as Margin)</t>
-  </si>
-  <si>
-    <t>Money Market Instruments</t>
-  </si>
-  <si>
-    <t>Certificate of Deposits</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A16GB1</t>
-  </si>
-  <si>
-    <t>CRISIL A1+</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE238AD6AJ8</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A16QQ4</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A16HP7</t>
-  </si>
-  <si>
-    <t>ICRA A1+</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda **</t>
-  </si>
-  <si>
-    <t>INE028A16FL7</t>
-  </si>
-  <si>
-    <t>FITCH A1+</t>
-  </si>
-  <si>
-    <t>Punjab National Bank **</t>
-  </si>
-  <si>
-    <t>INE160A16QP6</t>
-  </si>
-  <si>
-    <t>Bank Of India</t>
-  </si>
-  <si>
-    <t>INE084A16CQ6</t>
-  </si>
-  <si>
-    <t>INE238AD6827</t>
-  </si>
-  <si>
-    <t>INE028A16HM1</t>
-  </si>
-  <si>
-    <t>INE160A16OP1</t>
-  </si>
-  <si>
-    <t>INE040A16EP6</t>
-  </si>
-  <si>
-    <t>INE160A16PK9</t>
-  </si>
-  <si>
-    <t>IDFC First Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE092T16XR3</t>
+    <t>INE040A16GU1</t>
+  </si>
+  <si>
+    <t>INE562A16OP8</t>
+  </si>
+  <si>
+    <t>INE084A16DO9</t>
   </si>
   <si>
     <t>Karur Vysya Bank Ltd. **</t>
   </si>
   <si>
-    <t>INE036D16IA1</t>
-  </si>
-  <si>
-    <t>Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE084A16CX2</t>
-  </si>
-  <si>
-    <t>Union Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE692A16HR3</t>
-  </si>
-  <si>
-    <t>INE040A16GC9</t>
-  </si>
-  <si>
-    <t>Indian Bank **</t>
-  </si>
-  <si>
-    <t>INE562A16NU0</t>
-  </si>
-  <si>
-    <t>Punjab &amp; Sind Bank **</t>
-  </si>
-  <si>
-    <t>INE608A16RL1</t>
-  </si>
-  <si>
-    <t>INE692A16GZ8</t>
-  </si>
-  <si>
-    <t>RBL Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE976G16NY1</t>
-  </si>
-  <si>
-    <t>INE976G16NV7</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A16MT4</t>
+    <t>INE036D16IG8</t>
+  </si>
+  <si>
+    <t>INE976G16OC5</t>
+  </si>
+  <si>
+    <t>INE036D16IH6</t>
+  </si>
+  <si>
+    <t>Federal Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE171A16MX6</t>
   </si>
   <si>
     <t>Equitas Small Finance Bank Ltd. **</t>
   </si>
   <si>
-    <t>INE063P16AN9</t>
-  </si>
-  <si>
-    <t>INE692A16GY1</t>
-  </si>
-  <si>
-    <t>NABARD</t>
-  </si>
-  <si>
-    <t>INE261F16850</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India.</t>
-  </si>
-  <si>
-    <t>INE556F16AR4</t>
-  </si>
-  <si>
-    <t>INE040A16ER2</t>
-  </si>
-  <si>
-    <t>INE036D16IB9</t>
-  </si>
-  <si>
-    <t>INE028A16HI9</t>
+    <t>INE063P16AV2</t>
+  </si>
+  <si>
+    <t>DCB Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE503A16GZ7</t>
+  </si>
+  <si>
+    <t>INE063P16AU4</t>
+  </si>
+  <si>
+    <t>INE503A16HA8</t>
+  </si>
+  <si>
+    <t>AU Small Finance Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE949L16CT1</t>
+  </si>
+  <si>
+    <t>INE028A16IJ5</t>
+  </si>
+  <si>
+    <t>Commercial Papers</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India. **</t>
+  </si>
+  <si>
+    <t>INE556F14LB0</t>
+  </si>
+  <si>
+    <t>Reliance Retail Ventures Ltd **</t>
+  </si>
+  <si>
+    <t>INE929O14DK9</t>
+  </si>
+  <si>
+    <t>INE929O14DL7</t>
+  </si>
+  <si>
+    <t>INE556F14LD6</t>
   </si>
   <si>
     <t>NABARD **</t>
   </si>
   <si>
-    <t>INE261F16843</t>
-  </si>
-  <si>
-    <t>INE028A16HQ2</t>
-  </si>
-  <si>
-    <t>INE238AD6694</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE095A16V79</t>
-  </si>
-  <si>
-    <t>INE040A16EN1</t>
-  </si>
-  <si>
-    <t>INE261F16819</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A16V46</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A16EX5</t>
-  </si>
-  <si>
-    <t>Canara Bank **</t>
-  </si>
-  <si>
-    <t>INE476A16XV0</t>
-  </si>
-  <si>
-    <t>INE160A16PE2</t>
-  </si>
-  <si>
-    <t>INE476A16YZ9</t>
-  </si>
-  <si>
-    <t>INE261F16793</t>
-  </si>
-  <si>
-    <t>INE562A16MR8</t>
-  </si>
-  <si>
-    <t>INE692A16HZ6</t>
-  </si>
-  <si>
-    <t>INE160A16QH3</t>
-  </si>
-  <si>
-    <t>INE476A16ZM4</t>
-  </si>
-  <si>
-    <t>INE476A16ZC5</t>
-  </si>
-  <si>
-    <t>INE040A16FZ2</t>
-  </si>
-  <si>
-    <t>INE040A16EU6</t>
-  </si>
-  <si>
-    <t>INE095A16W11</t>
-  </si>
-  <si>
-    <t>INE160A16OM8</t>
-  </si>
-  <si>
-    <t>Commercial Papers</t>
-  </si>
-  <si>
-    <t>INE261F14MP5</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India. **</t>
-  </si>
-  <si>
-    <t>INE556F14KU2</t>
-  </si>
-  <si>
-    <t>Reliance Retail Ventures Ltd **</t>
-  </si>
-  <si>
-    <t>INE929O14CT2</t>
-  </si>
-  <si>
-    <t>INE929O14CU0</t>
-  </si>
-  <si>
-    <t>INE929O14CS4</t>
-  </si>
-  <si>
-    <t>INE556F14KS6</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd. **</t>
-  </si>
-  <si>
-    <t>INE018A14LG1</t>
-  </si>
-  <si>
-    <t>INE261F14MK6</t>
-  </si>
-  <si>
-    <t>INE477A14DI2</t>
-  </si>
-  <si>
-    <t>INE556F14KR8</t>
-  </si>
-  <si>
-    <t>INE929O14CZ9</t>
-  </si>
-  <si>
-    <t>INE261F14MV3</t>
+    <t>INE261F14NT5</t>
+  </si>
+  <si>
+    <t>Bajaj Financial Security Ltd. **</t>
+  </si>
+  <si>
+    <t>INE01C314BI6</t>
+  </si>
+  <si>
+    <t>Reliance Jio Infocomm Ltd. **</t>
+  </si>
+  <si>
+    <t>INE110L14TH4</t>
+  </si>
+  <si>
+    <t>INE261F14NS7</t>
+  </si>
+  <si>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E14SU7</t>
+  </si>
+  <si>
+    <t>Bharat Heavy Electricals Ltd. **</t>
+  </si>
+  <si>
+    <t>INE257A14953</t>
+  </si>
+  <si>
+    <t>Kotak Securities Ltd.</t>
+  </si>
+  <si>
+    <t>INE028E14QR8</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE002A14LD2</t>
+  </si>
+  <si>
+    <t>Bajaj Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE296A14ZZ3</t>
+  </si>
+  <si>
+    <t>INE929O14DI3</t>
+  </si>
+  <si>
+    <t>Aditya Birla Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE831R14ES1</t>
+  </si>
+  <si>
+    <t>INE929O14DH5</t>
+  </si>
+  <si>
+    <t>INE257A14946</t>
+  </si>
+  <si>
+    <t>INE110L14TN2</t>
+  </si>
+  <si>
+    <t>INE377Y14BH0</t>
+  </si>
+  <si>
+    <t>Birla Group Holdings Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE09OL14HJ7</t>
+  </si>
+  <si>
+    <t>INE261F14NJ6</t>
   </si>
   <si>
     <t>Sikka Ports &amp; Terminals Ltd. **</t>
   </si>
   <si>
-    <t>INE941D14618</t>
+    <t>INE941D14675</t>
+  </si>
+  <si>
+    <t>Sundaram Home Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE667F14GL4</t>
+  </si>
+  <si>
+    <t>INE01C314908</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE134E14AW8</t>
+  </si>
+  <si>
+    <t>TVS Credit Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE729N14II8</t>
+  </si>
+  <si>
+    <t>Panatone Finvest Ltd. **</t>
+  </si>
+  <si>
+    <t>INE116F14208</t>
+  </si>
+  <si>
+    <t>Aditya Birla Real Estate Ltd. **</t>
+  </si>
+  <si>
+    <t>INE055A14KF7</t>
+  </si>
+  <si>
+    <t>Tata Realty &amp; Infrastructure Ltd. **</t>
+  </si>
+  <si>
+    <t>INE371K14CV1</t>
+  </si>
+  <si>
+    <t>INE261F14NN8</t>
+  </si>
+  <si>
+    <t>SBICAP Securities Ltd **</t>
+  </si>
+  <si>
+    <t>INE212K14AQ1</t>
+  </si>
+  <si>
+    <t>Motilal Oswal Financial Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE338I14JR7</t>
+  </si>
+  <si>
+    <t>INE261F14NH0</t>
+  </si>
+  <si>
+    <t>Nirma Ltd. **</t>
+  </si>
+  <si>
+    <t>INE091A14EJ7</t>
+  </si>
+  <si>
+    <t>Julius Baer Capital (India) Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE824H14QT9</t>
+  </si>
+  <si>
+    <t>Axis Securities Ltd. **</t>
+  </si>
+  <si>
+    <t>INE110O14FF1</t>
+  </si>
+  <si>
+    <t>NTPC Ltd. **</t>
+  </si>
+  <si>
+    <t>INE733E14BT1</t>
+  </si>
+  <si>
+    <t>INE941D14683</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE242A14XV1</t>
+  </si>
+  <si>
+    <t>INE338I14KE3</t>
+  </si>
+  <si>
+    <t>Tata Capital Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE033L14OB2</t>
+  </si>
+  <si>
+    <t>INE831R14EY9</t>
+  </si>
+  <si>
+    <t>INE110O14FD6</t>
   </si>
   <si>
     <t>HDFC Securities Ltd **</t>
   </si>
   <si>
-    <t>INE700G14MT2</t>
-  </si>
-  <si>
-    <t>INE081A14FH9</t>
-  </si>
-  <si>
-    <t>Axis Securities Ltd. **</t>
-  </si>
-  <si>
-    <t>INE110O14EK4</t>
-  </si>
-  <si>
-    <t>INE110O14CU7</t>
-  </si>
-  <si>
-    <t>Birla Group Holdings Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE09OL14GE0</t>
-  </si>
-  <si>
-    <t>Bajaj Financial Security Ltd. **</t>
-  </si>
-  <si>
-    <t>INE01C314AZ2</t>
-  </si>
-  <si>
-    <t>Aditya Birla Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE831R14EK8</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd. **</t>
-  </si>
-  <si>
-    <t>INE481G14FC9</t>
-  </si>
-  <si>
-    <t>INE01C314AV1</t>
+    <t>INE700G14NX2</t>
   </si>
   <si>
     <t>Kotak Securities Ltd. **</t>
   </si>
   <si>
-    <t>INE028E14PX8</t>
-  </si>
-  <si>
-    <t>Julius Baer Capital (India) Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE824H14QY9</t>
-  </si>
-  <si>
-    <t>INE700G14MV8</t>
-  </si>
-  <si>
-    <t>INE261F14ML4</t>
-  </si>
-  <si>
-    <t>INE028E14PO7</t>
-  </si>
-  <si>
-    <t>INE028E14PQ2</t>
-  </si>
-  <si>
-    <t>INE09OL14GF7</t>
-  </si>
-  <si>
-    <t>Bajaj Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE377Y14AY7</t>
-  </si>
-  <si>
-    <t>INE110O14EO6</t>
-  </si>
-  <si>
-    <t>INE261F14MS9</t>
-  </si>
-  <si>
-    <t>INE700G14MY2</t>
-  </si>
-  <si>
-    <t>INE700G14MZ9</t>
-  </si>
-  <si>
-    <t>Aditya Birla Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE860H144R4</t>
-  </si>
-  <si>
-    <t>INE556F14KG1</t>
-  </si>
-  <si>
-    <t>Bajaj Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE296A14XX3</t>
-  </si>
-  <si>
-    <t>Reliance Retail Ventures Ltd</t>
-  </si>
-  <si>
-    <t>INE929O14CP0</t>
-  </si>
-  <si>
-    <t>Poonawalla Fincorp Ltd **</t>
-  </si>
-  <si>
-    <t>INE511C14XP7</t>
+    <t>INE028E14QV0</t>
+  </si>
+  <si>
+    <t>Tata Housing Development Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE582L14IE4</t>
+  </si>
+  <si>
+    <t>Barclays Investments &amp; Loans (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE704I14JG3</t>
+  </si>
+  <si>
+    <t>INE09OL14FY0</t>
+  </si>
+  <si>
+    <t>INE110O14FC8</t>
+  </si>
+  <si>
+    <t>INE028E14QQ0</t>
+  </si>
+  <si>
+    <t>INE824H14RP5</t>
+  </si>
+  <si>
+    <t>CESC Ltd. **</t>
+  </si>
+  <si>
+    <t>INE486A14FI8</t>
+  </si>
+  <si>
+    <t>APL Apollo Tubes Ltd. **</t>
+  </si>
+  <si>
+    <t>INE702C14CN1</t>
+  </si>
+  <si>
+    <t>INE028E14QS6</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd **</t>
+  </si>
+  <si>
+    <t>INE220B14BJ6</t>
+  </si>
+  <si>
+    <t>INE702C14CM3</t>
+  </si>
+  <si>
+    <t>INE377Y14BF4</t>
+  </si>
+  <si>
+    <t>Motilal oswal finvest Ltd **</t>
+  </si>
+  <si>
+    <t>INE01WN14BQ1</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE466L14EJ8</t>
+  </si>
+  <si>
+    <t>IGH Holdings Pvt Ltd. **</t>
+  </si>
+  <si>
+    <t>INE02FN14481</t>
+  </si>
+  <si>
+    <t>Bharti Telecom Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403D14577</t>
+  </si>
+  <si>
+    <t>Bajaj Auto Credit Ltd. **</t>
+  </si>
+  <si>
+    <t>INE18UV14018</t>
+  </si>
+  <si>
+    <t>INE700G14OI1</t>
+  </si>
+  <si>
+    <t>INE01C314BT3</t>
+  </si>
+  <si>
+    <t>INE466L14EL4</t>
+  </si>
+  <si>
+    <t>Alembic Pharmaceuticals Ltd. **</t>
+  </si>
+  <si>
+    <t>INE901L14BH4</t>
+  </si>
+  <si>
+    <t>Poonawalla Fincorp Ltd. **</t>
+  </si>
+  <si>
+    <t>INE511C14YI0</t>
+  </si>
+  <si>
+    <t>Minda Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE842C14107</t>
+  </si>
+  <si>
+    <t>INE338I14KF0</t>
+  </si>
+  <si>
+    <t>INE941D14691</t>
+  </si>
+  <si>
+    <t>PNB Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE572E14JU4</t>
+  </si>
+  <si>
+    <t>Tata Teleservices Ltd. **</t>
+  </si>
+  <si>
+    <t>INE037E14AS1</t>
+  </si>
+  <si>
+    <t>INE01C314BH8</t>
+  </si>
+  <si>
+    <t>INE704I14KB2</t>
+  </si>
+  <si>
+    <t>INE824H14RT7</t>
+  </si>
+  <si>
+    <t>SEIL Energy India Ltd. **</t>
+  </si>
+  <si>
+    <t>INE460M14735</t>
+  </si>
+  <si>
+    <t>Aditya Birla Money Ltd. **</t>
+  </si>
+  <si>
+    <t>INE865C14NJ1</t>
+  </si>
+  <si>
+    <t>Standard Chartered Capital Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403G14TB6</t>
+  </si>
+  <si>
+    <t>INE582L14IG9</t>
+  </si>
+  <si>
+    <t>INE09OL14HA6</t>
+  </si>
+  <si>
+    <t>JK Tyre &amp; Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE573A14714</t>
+  </si>
+  <si>
+    <t>INE842C14115</t>
+  </si>
+  <si>
+    <t>DCM Shriram Ltd. **</t>
+  </si>
+  <si>
+    <t>INE499A14CZ2</t>
+  </si>
+  <si>
+    <t>INE212K14AZ2</t>
+  </si>
+  <si>
+    <t>INE573A14706</t>
+  </si>
+  <si>
+    <t>INE831R14EV5</t>
+  </si>
+  <si>
+    <t>Godrej Agrovet Ltd. **</t>
+  </si>
+  <si>
+    <t>INE850D14TW1</t>
+  </si>
+  <si>
+    <t>INE499A14DA3</t>
+  </si>
+  <si>
+    <t>INE865C14NP8</t>
   </si>
   <si>
     <t>Network18 Media &amp; Investments Ltd. **</t>
   </si>
   <si>
-    <t>INE870H14TX8</t>
-  </si>
-  <si>
-    <t>Mirae Asset Capital Markets (India) Pvt Ltd **</t>
-  </si>
-  <si>
-    <t>INE0T2V14053</t>
-  </si>
-  <si>
-    <t>INE824H14QQ5</t>
-  </si>
-  <si>
-    <t>INE028E14PT6</t>
-  </si>
-  <si>
-    <t>INE01C314AY5</t>
+    <t>INE870H14VE4</t>
+  </si>
+  <si>
+    <t>360 ONE Prime Ltd **</t>
+  </si>
+  <si>
+    <t>INE248U14RN5</t>
   </si>
   <si>
     <t>SRF Ltd. **</t>
   </si>
   <si>
-    <t>INE647A14AR7</t>
-  </si>
-  <si>
-    <t>360 One Prime Ltd. **</t>
-  </si>
-  <si>
-    <t>INE248U14QO5</t>
-  </si>
-  <si>
-    <t>Barclays Investments &amp; Loans (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE704I14JP4</t>
-  </si>
-  <si>
-    <t>INE870H14TW0</t>
-  </si>
-  <si>
-    <t>INE110O14EF4</t>
-  </si>
-  <si>
-    <t>Tata Projects Ltd. **</t>
-  </si>
-  <si>
-    <t>INE725H14CL5</t>
-  </si>
-  <si>
-    <t>Reliance Jio Infocomm Ltd. **</t>
-  </si>
-  <si>
-    <t>INE110L14SR5</t>
-  </si>
-  <si>
-    <t>INE110O14CE1</t>
-  </si>
-  <si>
-    <t>Aditya Birla Money Ltd. **</t>
-  </si>
-  <si>
-    <t>INE865C14MP0</t>
-  </si>
-  <si>
-    <t>INE028E14ON2</t>
-  </si>
-  <si>
-    <t>INE824H14QV5</t>
-  </si>
-  <si>
-    <t>Minda Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE842C14081</t>
-  </si>
-  <si>
-    <t>INE929O14CY2</t>
-  </si>
-  <si>
-    <t>SEIL Energy India Ltd. **</t>
-  </si>
-  <si>
-    <t>INE460M14701</t>
-  </si>
-  <si>
-    <t>INE700G14NC6</t>
-  </si>
-  <si>
-    <t>INE110O14ER9</t>
-  </si>
-  <si>
-    <t>INE248U14QV0</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE338I14IP3</t>
-  </si>
-  <si>
-    <t>Godrej Properties Ltd. **</t>
-  </si>
-  <si>
-    <t>INE484J14VS0</t>
-  </si>
-  <si>
-    <t>Aditya Birla Real Estate Ltd. **</t>
-  </si>
-  <si>
-    <t>INE055A14KB6</t>
-  </si>
-  <si>
-    <t>NU Vista Ltd **</t>
-  </si>
-  <si>
-    <t>INE973U14193</t>
-  </si>
-  <si>
-    <t>Godrej Housing Finance Ltd **</t>
-  </si>
-  <si>
-    <t>INE02JD14492</t>
-  </si>
-  <si>
-    <t>JK Tyre &amp; Industries Ltd. **</t>
-  </si>
-  <si>
-    <t>INE573A14664</t>
-  </si>
-  <si>
-    <t>CARE A1+</t>
-  </si>
-  <si>
-    <t>INE700G14ME4</t>
-  </si>
-  <si>
-    <t>INE870H14TY6</t>
-  </si>
-  <si>
-    <t>HDFC Securities Ltd</t>
-  </si>
-  <si>
-    <t>INE700G14MD6</t>
-  </si>
-  <si>
-    <t>INE573A14672</t>
-  </si>
-  <si>
-    <t>INE01C314AR9</t>
-  </si>
-  <si>
-    <t>Motilal Oswal Financial Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE338I14IT5</t>
-  </si>
-  <si>
-    <t>Nuvoco Vistas Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE118D14886</t>
-  </si>
-  <si>
-    <t>INE700G14MI5</t>
-  </si>
-  <si>
-    <t>INE484J14WK5</t>
-  </si>
-  <si>
-    <t>INE484J14VV4</t>
-  </si>
-  <si>
-    <t>Tata Housing Development Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE582L14HV0</t>
-  </si>
-  <si>
-    <t>INE118D14894</t>
-  </si>
-  <si>
-    <t>INE01C314AT5</t>
-  </si>
-  <si>
-    <t>Infina Finance Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE879F14JR6</t>
-  </si>
-  <si>
-    <t>INE460M14693</t>
-  </si>
-  <si>
-    <t>INE647A14AQ9</t>
-  </si>
-  <si>
-    <t>INE110O14EM0</t>
-  </si>
-  <si>
-    <t>INE09OL14EU1</t>
-  </si>
-  <si>
-    <t>Redington Ltd. **</t>
-  </si>
-  <si>
-    <t>INE891D14ZN1</t>
-  </si>
-  <si>
-    <t>INE842C14099</t>
-  </si>
-  <si>
-    <t>INE865C14MW6</t>
-  </si>
-  <si>
-    <t>INE879F14JE4</t>
-  </si>
-  <si>
-    <t>Tata Realty &amp; Infrastructure Ltd. **</t>
-  </si>
-  <si>
-    <t>INE371K14CN8</t>
-  </si>
-  <si>
-    <t>360 One Wam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE466L14EA7</t>
+    <t>INE647A14AV9</t>
+  </si>
+  <si>
+    <t>INE02FN14507</t>
+  </si>
+  <si>
+    <t>INE110O14EY5</t>
+  </si>
+  <si>
+    <t>Godrej Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE02KN14523</t>
+  </si>
+  <si>
+    <t>INE02KN14515</t>
+  </si>
+  <si>
+    <t>INE02FN14499</t>
+  </si>
+  <si>
+    <t>INE212K14AY5</t>
   </si>
   <si>
     <t>Mahindra Lifespace Developers Ltd. **</t>
   </si>
   <si>
-    <t>INE813A14268</t>
-  </si>
-  <si>
-    <t>INE484J14WJ7</t>
+    <t>INE813A14326</t>
+  </si>
+  <si>
+    <t>Deutsche Investments India Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE144H14HO2</t>
+  </si>
+  <si>
+    <t>SBI Global Factors Ltd. **</t>
+  </si>
+  <si>
+    <t>INE912E14ME0</t>
+  </si>
+  <si>
+    <t>INE941D14667</t>
+  </si>
+  <si>
+    <t>Cholamandalam Securities Ltd. **</t>
+  </si>
+  <si>
+    <t>INE04JX14082</t>
+  </si>
+  <si>
+    <t>Pilani Investment &amp; Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE417C14918</t>
   </si>
   <si>
     <t>Pilani Investment &amp; Industries Corp Ltd **</t>
   </si>
   <si>
-    <t>INE417C14843</t>
-  </si>
-  <si>
-    <t>INE028E14OD3</t>
-  </si>
-  <si>
-    <t>INE865C14MR6</t>
-  </si>
-  <si>
-    <t>INE813A14276</t>
-  </si>
-  <si>
-    <t>INE09OL14GD2</t>
-  </si>
-  <si>
-    <t>Nexus Select Trust Ltd. **</t>
-  </si>
-  <si>
-    <t>INE0NDH14049</t>
-  </si>
-  <si>
-    <t>Cholamandalam Securities Ltd **</t>
-  </si>
-  <si>
-    <t>INE04JX14066</t>
-  </si>
-  <si>
-    <t>INE02JD14567</t>
-  </si>
-  <si>
-    <t>INE973U14201</t>
-  </si>
-  <si>
-    <t>JK Cement Ltd. **</t>
-  </si>
-  <si>
-    <t>INE823G14AK6</t>
-  </si>
-  <si>
-    <t>INE823G14AL4</t>
-  </si>
-  <si>
-    <t>INE823G14AM2</t>
-  </si>
-  <si>
-    <t>Toyota Financial Services India **</t>
-  </si>
-  <si>
-    <t>INE692Q14BC9</t>
-  </si>
-  <si>
-    <t>INE261F14MN0</t>
-  </si>
-  <si>
-    <t>IGH Holdings Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE02FN14358</t>
-  </si>
-  <si>
-    <t>Panatone Finvest Ltd. **</t>
-  </si>
-  <si>
-    <t>INE116F14190</t>
-  </si>
-  <si>
-    <t>INE484J14VW2</t>
-  </si>
-  <si>
-    <t>INE700G14MH7</t>
-  </si>
-  <si>
-    <t>Standard Chartered Securities India Ltd **</t>
-  </si>
-  <si>
-    <t>INE472H14284</t>
-  </si>
-  <si>
-    <t>INE865C14MQ8</t>
-  </si>
-  <si>
-    <t>INE870H14UH9</t>
-  </si>
-  <si>
-    <t>INE860H143N5</t>
+    <t>INE417C14942</t>
+  </si>
+  <si>
+    <t>HSBC Invest Direct Financial Services (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE790I14FW7</t>
+  </si>
+  <si>
+    <t>Triveni Engineering &amp; Industries Ltd. **</t>
+  </si>
+  <si>
+    <t>INE256C14HD8</t>
+  </si>
+  <si>
+    <t>INE256C14HF3</t>
+  </si>
+  <si>
+    <t>INE842C14123</t>
+  </si>
+  <si>
+    <t>INE256C14HC0</t>
+  </si>
+  <si>
+    <t>Nexus Select Trust **</t>
+  </si>
+  <si>
+    <t>INE0NDH14064</t>
+  </si>
+  <si>
+    <t>INE850D14TY7</t>
+  </si>
+  <si>
+    <t>INE556F14KY4</t>
+  </si>
+  <si>
+    <t>INE929O14DF9</t>
+  </si>
+  <si>
+    <t>INE256C14HE6</t>
   </si>
   <si>
     <t>Bills Rediscounted</t>
@@ -925,70 +781,70 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024X433</t>
-  </si>
-  <si>
-    <t>IN002024X342</t>
-  </si>
-  <si>
-    <t>IN002024X334</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>IN002024X318</t>
-  </si>
-  <si>
-    <t>IN002024X359</t>
+    <t>IN002025X083</t>
+  </si>
+  <si>
+    <t>IN002024X508</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>IN002025X059</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
+  </si>
+  <si>
+    <t>182 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Y423</t>
+  </si>
+  <si>
+    <t>IN002025X067</t>
+  </si>
+  <si>
+    <t>IN002025X018</t>
+  </si>
+  <si>
+    <t>IN002024Y373</t>
+  </si>
+  <si>
+    <t>364 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Z172</t>
+  </si>
+  <si>
+    <t>IN002024Z180</t>
+  </si>
+  <si>
+    <t>IN002024X490</t>
   </si>
   <si>
     <t>Reverse Repo</t>
   </si>
   <si>
-    <t>Reverse Repo ( 3/20/2025 )</t>
-  </si>
-  <si>
-    <t>GSECREPO0556</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 2/11/2025 )</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 3/10/2025 )</t>
-  </si>
-  <si>
-    <t>GSECREPO0540</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 3/12/2025 )</t>
-  </si>
-  <si>
-    <t>GSECREPO0538</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 2/28/2025 )</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 3/21/2025 )</t>
-  </si>
-  <si>
-    <t>GSECREPO0557</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 2/4/2025 )</t>
-  </si>
-  <si>
-    <t>Reverse Repo ( 3/13/2025 )</t>
-  </si>
-  <si>
-    <t>GSECREPO0542</t>
+    <t>Reverse Repo (19-6-2025)</t>
+  </si>
+  <si>
+    <t>Reverse Repo (21-8-2025)</t>
+  </si>
+  <si>
+    <t>GSECREPO0647</t>
+  </si>
+  <si>
+    <t>Reverse Repo (17-6-2025)</t>
+  </si>
+  <si>
+    <t>Reverse Repo (20-6-2025)</t>
+  </si>
+  <si>
+    <t>GSECREPO0643</t>
+  </si>
+  <si>
+    <t>Reverse Repo (19-8-2025)</t>
   </si>
   <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
@@ -1024,22 +880,16 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>“This scheme has exposure to floating rate instruments and / or interest rate derivatives. The duration of these instruments is linked to the interest rate reset period. The interest rate risk in a floating rate instrument or in a fixed rate instrument hedged with derivatives is likely to be lesser than that in an equivalent maturity fixed rate instrument. Under some market circumstances the volatility may be of an order greater than what may ordinarily be expected considering only its duration. Hence investors are recommended to consider the unadjusted portfolio maturity of the scheme as well and exercise adequate due diligence when deciding to make their investments”.</t>
-  </si>
-  <si>
     <t>Scheme Riskometer</t>
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - CRISIL Liquid Debt A-I Index</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1089,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1325,10 +1175,6 @@
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
       <protection/>
     </xf>
   </cellXfs>
@@ -1417,13 +1263,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>251</xdr:row>
+      <xdr:row>213</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>261</xdr:row>
+      <xdr:row>223</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1441,8 +1287,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="48748950"/>
-          <a:ext cx="4019550" cy="1905000"/>
+          <a:off x="666750" y="41033700"/>
+          <a:ext cx="3657600" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1456,13 +1302,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>266</xdr:row>
+      <xdr:row>228</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>276</xdr:row>
+      <xdr:row>238</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1480,8 +1326,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="51606450"/>
-          <a:ext cx="4019550" cy="1905000"/>
+          <a:off x="666750" y="43891200"/>
+          <a:ext cx="3657600" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1814,15 +1660,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J265"/>
+  <dimension ref="B1:J226"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="60.285714285714285" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="54.857142857142854" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.285714285714285" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.285714285714286" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.571428571428571" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
@@ -1914,10 +1760,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>211947.89000000004</v>
+        <v>36029.88</v>
       </c>
       <c r="H5" s="10">
-        <v>0.037190805732500005</v>
+        <v>0.007205989243699999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1951,10 +1797,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>211947.89000000004</v>
+        <v>36029.88</v>
       </c>
       <c r="H7" s="10">
-        <v>0.037190805732500005</v>
+        <v>0.007205989243699999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1988,10 +1834,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>42577.07</v>
+        <v>502.79</v>
       </c>
       <c r="H9" s="10">
-        <v>0.0074710606415000005</v>
+        <v>0.0001005581848</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -2008,22 +1854,22 @@
         <v>17</v>
       </c>
       <c r="D10" s="14">
-        <v>8.120000000000001</v>
+        <v>8.290000000000001</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="15">
-        <v>40000000</v>
+        <v>500000</v>
       </c>
       <c r="G10" s="16">
-        <v>40074.96</v>
+        <v>502.79</v>
       </c>
       <c r="H10" s="17">
-        <v>0.0070320117464</v>
+        <v>0.0001005581848</v>
       </c>
       <c r="I10" s="16">
-        <v>6.64</v>
+        <v>5.78</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -2031,65 +1877,65 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="15" customHeight="1">
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="9">
+        <v>35527.09</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.007105431058899999</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="15" customHeight="1">
+      <c r="B13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="14">
-        <v>8.040000000000001</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="15">
-        <v>2500000</v>
-      </c>
-      <c r="G11" s="16">
-        <v>2502.11</v>
-      </c>
-      <c r="H11" s="17">
-        <v>0.0004390488951</v>
-      </c>
-      <c r="I11" s="16">
-        <v>6.63</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="15" customHeight="1">
-      <c r="B12" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="15" customHeight="1">
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="9">
-        <v>169370.82000000004</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0.029719745091</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>13</v>
+      <c r="D13" s="14">
+        <v>7.13</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="15">
+        <v>2050</v>
+      </c>
+      <c r="G13" s="16">
+        <v>20516.42</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0.0041032915414</v>
+      </c>
+      <c r="I13" s="16">
+        <v>6.33</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -2097,28 +1943,28 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="14">
+        <v>7.42</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="14">
-        <v>5.9943</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="F14" s="15">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="16">
-        <v>34933.36</v>
+        <v>10012.73</v>
       </c>
       <c r="H14" s="17">
-        <v>0.006129807687</v>
+        <v>0.0020025496804</v>
       </c>
       <c r="I14" s="16">
-        <v>7.40</v>
+        <v>6.39</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -2132,22 +1978,22 @@
         <v>26</v>
       </c>
       <c r="D15" s="14">
-        <v>7.70</v>
+        <v>6.25</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F15" s="15">
-        <v>3250</v>
+        <v>500</v>
       </c>
       <c r="G15" s="16">
-        <v>32482.29</v>
+        <v>4997.94</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0056997148551</v>
+        <v>0.0009995898371</v>
       </c>
       <c r="I15" s="16">
-        <v>7.96</v>
+        <v>6.65</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -2155,57 +2001,36 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15" customHeight="1">
+      <c r="B17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="14">
-        <v>7.79</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="15">
-        <v>26500</v>
-      </c>
-      <c r="G16" s="16">
-        <v>26490.94</v>
-      </c>
-      <c r="H16" s="17">
-        <v>0.0046484039224</v>
-      </c>
-      <c r="I16" s="16">
-        <v>7.65</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="15" customHeight="1">
-      <c r="B17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="14">
-        <v>8.11</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G17" s="16">
-        <v>20000.1</v>
-      </c>
-      <c r="H17" s="17">
-        <v>0.00350944675</v>
-      </c>
-      <c r="I17" s="16">
-        <v>7.78</v>
+      <c r="H17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -2213,57 +2038,36 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="14">
-        <v>6.70</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G18" s="16">
-        <v>19981.94</v>
-      </c>
-      <c r="H18" s="17">
-        <v>0.0035062601883</v>
-      </c>
-      <c r="I18" s="16">
-        <v>7.61</v>
+        <v>13</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
-      <c r="B19" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="14">
-        <v>6.35</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="15">
-        <v>1250</v>
-      </c>
-      <c r="G19" s="16">
-        <v>12489.76</v>
-      </c>
-      <c r="H19" s="17">
-        <v>0.002191596424</v>
-      </c>
-      <c r="I19" s="16">
-        <v>7.94</v>
+      <c r="B19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -2271,57 +2075,36 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="14">
-        <v>8.25</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="15">
-        <v>800000</v>
-      </c>
-      <c r="G20" s="16">
-        <v>7998.39</v>
-      </c>
-      <c r="H20" s="17">
-        <v>0.0014034891721</v>
-      </c>
-      <c r="I20" s="16">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
-      <c r="B21" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="14">
-        <v>8.59</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="15">
-        <v>750</v>
-      </c>
-      <c r="G21" s="16">
-        <v>7498.32</v>
-      </c>
-      <c r="H21" s="17">
-        <v>0.001315741159</v>
-      </c>
-      <c r="I21" s="16">
-        <v>8.82</v>
+      <c r="B21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -2329,57 +2112,36 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="14">
-        <v>7.70</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="15">
-        <v>500</v>
-      </c>
-      <c r="G22" s="16">
-        <v>4997.37</v>
-      </c>
-      <c r="H22" s="17">
-        <v>0.0008768958107</v>
-      </c>
-      <c r="I22" s="16">
-        <v>7.66</v>
+        <v>13</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
-      <c r="B23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="14">
-        <v>7.40</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="15">
-        <v>250</v>
-      </c>
-      <c r="G23" s="16">
-        <v>2498.35</v>
-      </c>
-      <c r="H23" s="17">
-        <v>0.0004383891224</v>
-      </c>
-      <c r="I23" s="16">
-        <v>7.87</v>
+      <c r="B23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -2395,7 +2157,7 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>13</v>
@@ -2410,10 +2172,10 @@
         <v>13</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>13</v>
@@ -2432,7 +2194,7 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>13</v>
@@ -2447,10 +2209,10 @@
         <v>13</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>13</v>
@@ -2469,7 +2231,7 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>13</v>
@@ -2483,11 +2245,11 @@
       <c r="F29" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>48</v>
+      <c r="G29" s="9">
+        <v>5318068.580000002</v>
+      </c>
+      <c r="H29" s="10">
+        <v>1.0636156708016993</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>13</v>
@@ -2506,7 +2268,7 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>13</v>
@@ -2520,11 +2282,11 @@
       <c r="F31" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>48</v>
+      <c r="G31" s="9">
+        <v>1220257.8600000003</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.2440520205401</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>13</v>
@@ -2535,36 +2297,57 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="15">
+        <v>45000</v>
+      </c>
+      <c r="G32" s="16">
+        <v>224342.78</v>
+      </c>
+      <c r="H32" s="17">
+        <v>0.0448686384636</v>
+      </c>
+      <c r="I32" s="16">
+        <v>6.29</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
-      <c r="B33" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>13</v>
+      <c r="B33" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="15">
+        <v>30000</v>
+      </c>
+      <c r="G33" s="16">
+        <v>147803.25</v>
+      </c>
+      <c r="H33" s="17">
+        <v>0.0295607043293</v>
+      </c>
+      <c r="I33" s="16">
+        <v>6.16</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2572,36 +2355,57 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>13</v>
+        <v>41</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="15">
+        <v>20000</v>
+      </c>
+      <c r="G34" s="16">
+        <v>98768.50</v>
+      </c>
+      <c r="H34" s="17">
+        <v>0.0197537363052</v>
+      </c>
+      <c r="I34" s="16">
+        <v>6.15</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
-      <c r="B35" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>13</v>
+      <c r="B35" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="15">
+        <v>20000</v>
+      </c>
+      <c r="G35" s="16">
+        <v>98677.50</v>
+      </c>
+      <c r="H35" s="17">
+        <v>0.0197355362717</v>
+      </c>
+      <c r="I35" s="16">
+        <v>6.12</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2609,36 +2413,57 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>13</v>
+        <v>45</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="15">
+        <v>15000</v>
+      </c>
+      <c r="G36" s="16">
+        <v>74155.28</v>
+      </c>
+      <c r="H36" s="17">
+        <v>0.0148310832579</v>
+      </c>
+      <c r="I36" s="16">
+        <v>6.11</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
-      <c r="B37" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="9">
-        <v>5022276.500000002</v>
-      </c>
-      <c r="H37" s="10">
-        <v>0.8812661907033997</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>13</v>
+      <c r="B37" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="15">
+        <v>13000</v>
+      </c>
+      <c r="G37" s="16">
+        <v>64896.46</v>
+      </c>
+      <c r="H37" s="17">
+        <v>0.0129793158545</v>
+      </c>
+      <c r="I37" s="16">
+        <v>6.47</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2646,36 +2471,57 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>13</v>
+        <v>51</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="15">
+        <v>11000</v>
+      </c>
+      <c r="G38" s="16">
+        <v>54256.46</v>
+      </c>
+      <c r="H38" s="17">
+        <v>0.0108513119435</v>
+      </c>
+      <c r="I38" s="16">
+        <v>6.10</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="9">
-        <v>1895966.7699999996</v>
-      </c>
-      <c r="H39" s="10">
-        <v>0.33268805751770003</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>13</v>
+      <c r="B39" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="15">
+        <v>10000</v>
+      </c>
+      <c r="G39" s="16">
+        <v>49845.05</v>
+      </c>
+      <c r="H39" s="17">
+        <v>0.0099690283219</v>
+      </c>
+      <c r="I39" s="16">
+        <v>6.31</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2683,28 +2529,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F40" s="15">
-        <v>37000</v>
+        <v>10000</v>
       </c>
       <c r="G40" s="16">
-        <v>183281.91</v>
+        <v>49744.45</v>
       </c>
       <c r="H40" s="17">
-        <v>0.032160744366</v>
+        <v>0.009948908285</v>
       </c>
       <c r="I40" s="16">
-        <v>7.28</v>
+        <v>6.25</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2712,28 +2558,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F41" s="15">
-        <v>21200</v>
+        <v>10000</v>
       </c>
       <c r="G41" s="16">
-        <v>104074.09</v>
+        <v>49737.25</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0182620325356</v>
+        <v>0.0099474682823</v>
       </c>
       <c r="I41" s="16">
-        <v>7.51</v>
+        <v>6.22</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2741,28 +2587,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F42" s="15">
-        <v>19000</v>
+        <v>10000</v>
       </c>
       <c r="G42" s="16">
-        <v>93985.02</v>
+        <v>49432.25</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0164916886912</v>
+        <v>0.0098864681702</v>
       </c>
       <c r="I42" s="16">
-        <v>7.30</v>
+        <v>6.17</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2770,28 +2616,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F43" s="15">
-        <v>18500</v>
+        <v>8000</v>
       </c>
       <c r="G43" s="16">
-        <v>91677.21</v>
+        <v>39930.24</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0160867339008</v>
+        <v>0.0079860626775</v>
       </c>
       <c r="I43" s="16">
-        <v>7.28</v>
+        <v>6.38</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2799,28 +2645,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F44" s="15">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="G44" s="16">
-        <v>79415.52</v>
+        <v>39886.52</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0139351572526</v>
+        <v>0.0079773186614</v>
       </c>
       <c r="I44" s="16">
-        <v>7.26</v>
+        <v>6.49</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2828,28 +2674,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F45" s="15">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="G45" s="16">
-        <v>74301.6</v>
+        <v>39881.12</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0130378102431</v>
+        <v>0.0079762386594</v>
       </c>
       <c r="I45" s="16">
-        <v>7.30</v>
+        <v>6.40</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2857,28 +2703,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F46" s="15">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="G46" s="16">
-        <v>69680.38</v>
+        <v>29568.54</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0122269180221</v>
+        <v>0.0059137188687</v>
       </c>
       <c r="I46" s="16">
-        <v>7.28</v>
+        <v>6.19</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2886,28 +2732,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F47" s="15">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="G47" s="16">
-        <v>69624.03</v>
+        <v>24964.25</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0122170302053</v>
+        <v>0.0049928591763</v>
       </c>
       <c r="I47" s="16">
-        <v>7.30</v>
+        <v>6.54</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2918,25 +2764,25 @@
         <v>66</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F48" s="15">
-        <v>14000</v>
+        <v>4500</v>
       </c>
       <c r="G48" s="16">
-        <v>68945.31</v>
+        <v>22464.09</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0120979342159</v>
+        <v>0.0044928262573</v>
       </c>
       <c r="I48" s="16">
-        <v>7.45</v>
+        <v>6.49</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2944,28 +2790,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F49" s="15">
-        <v>13000</v>
+        <v>4000</v>
       </c>
       <c r="G49" s="16">
-        <v>64509.77</v>
+        <v>19967.82</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0113196235355</v>
+        <v>0.0039935713397</v>
       </c>
       <c r="I49" s="16">
-        <v>7.30</v>
+        <v>6.54</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2973,28 +2819,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F50" s="15">
-        <v>12500</v>
+        <v>4000</v>
       </c>
       <c r="G50" s="16">
-        <v>62165.25</v>
+        <v>19707.36</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0109082271878</v>
+        <v>0.003941479244</v>
       </c>
       <c r="I50" s="16">
-        <v>7.28</v>
+        <v>6.61</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -3002,28 +2848,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F51" s="15">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G51" s="16">
-        <v>49810.70</v>
+        <v>14796.96</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0087403562599</v>
+        <v>0.002959397439</v>
       </c>
       <c r="I51" s="16">
-        <v>7.30</v>
+        <v>6.34</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -3031,28 +2877,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F52" s="15">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="G52" s="16">
-        <v>49808.80</v>
+        <v>7431.73</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0087400228641</v>
+        <v>0.0014863487317</v>
       </c>
       <c r="I52" s="16">
-        <v>7.38</v>
+        <v>6.21</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -3060,57 +2906,36 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" s="15">
-        <v>10000</v>
-      </c>
-      <c r="G53" s="16">
-        <v>49604.65</v>
-      </c>
-      <c r="H53" s="17">
-        <v>0.0087042003655</v>
-      </c>
-      <c r="I53" s="16">
-        <v>7.46</v>
+        <v>13</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" s="15">
-        <v>10000</v>
-      </c>
-      <c r="G54" s="16">
-        <v>49565.05</v>
-      </c>
-      <c r="H54" s="17">
-        <v>0.0086972516957</v>
-      </c>
-      <c r="I54" s="16">
-        <v>7.28</v>
+      <c r="B54" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="9">
+        <v>3170142.729999999</v>
+      </c>
+      <c r="H54" s="10">
+        <v>0.6340297112712994</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -3118,28 +2943,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F55" s="15">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="G55" s="16">
-        <v>49545.45</v>
+        <v>149207.40</v>
       </c>
       <c r="H55" s="17">
-        <v>0.008693812455</v>
+        <v>0.0298415348454</v>
       </c>
       <c r="I55" s="16">
-        <v>7.28</v>
+        <v>6.26</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -3147,28 +2972,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F56" s="15">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="G56" s="16">
-        <v>49496.50</v>
+        <v>123450.63</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0086852231271</v>
+        <v>0.0246901713778</v>
       </c>
       <c r="I56" s="16">
-        <v>7.28</v>
+        <v>6.19</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -3176,28 +3001,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F57" s="15">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="G57" s="16">
-        <v>49395.10</v>
+        <v>123285.38</v>
       </c>
       <c r="H57" s="17">
-        <v>0.008667430321</v>
+        <v>0.024657121317</v>
       </c>
       <c r="I57" s="16">
-        <v>7.45</v>
+        <v>6.19</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -3205,28 +3030,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F58" s="15">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="G58" s="16">
-        <v>49386.25</v>
+        <v>123217.38</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0086658773986</v>
+        <v>0.024643521292</v>
       </c>
       <c r="I58" s="16">
-        <v>7.56</v>
+        <v>6.14</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -3234,28 +3059,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F59" s="15">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="G59" s="16">
-        <v>39793.64</v>
+        <v>98635</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0069826481153</v>
+        <v>0.0197270362561</v>
       </c>
       <c r="I59" s="16">
-        <v>7.28</v>
+        <v>6.16</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -3263,28 +3088,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F60" s="15">
-        <v>7500</v>
+        <v>16000</v>
       </c>
       <c r="G60" s="16">
-        <v>37194.98</v>
+        <v>79731.28</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0065266574507</v>
+        <v>0.0159462853075</v>
       </c>
       <c r="I60" s="16">
-        <v>7.68</v>
+        <v>6.84</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -3292,28 +3117,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F61" s="15">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="G61" s="16">
-        <v>34700.86</v>
+        <v>74841.83</v>
       </c>
       <c r="H61" s="17">
-        <v>0.0060890105725</v>
+        <v>0.0149683935102</v>
       </c>
       <c r="I61" s="16">
-        <v>7.68</v>
+        <v>6.43</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -3321,28 +3146,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F62" s="15">
-        <v>6500</v>
+        <v>15000</v>
       </c>
       <c r="G62" s="16">
-        <v>32261.94</v>
+        <v>74436.9</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0056610497189</v>
+        <v>0.0148874073614</v>
       </c>
       <c r="I62" s="16">
-        <v>7.28</v>
+        <v>6.28</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3350,28 +3175,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F63" s="15">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="G63" s="16">
-        <v>29924.64</v>
+        <v>74153.18</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0052509202751</v>
+        <v>0.0148306632571</v>
       </c>
       <c r="I63" s="16">
-        <v>7.66</v>
+        <v>6.13</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3379,28 +3204,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F64" s="15">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="G64" s="16">
-        <v>29857.08</v>
+        <v>64379.77</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0052390654232</v>
+        <v>0.0128759776646</v>
       </c>
       <c r="I64" s="16">
-        <v>7.28</v>
+        <v>6.64</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3408,28 +3233,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F65" s="15">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="G65" s="16">
-        <v>29731.68</v>
+        <v>59796.54</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0052170613021</v>
+        <v>0.0119593299799</v>
       </c>
       <c r="I65" s="16">
-        <v>7.32</v>
+        <v>6.90</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3437,28 +3262,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F66" s="15">
-        <v>5500</v>
+        <v>12000</v>
       </c>
       <c r="G66" s="16">
-        <v>27357.74</v>
+        <v>59769.78</v>
       </c>
       <c r="H66" s="17">
-        <v>0.004800502584</v>
+        <v>0.0119539779701</v>
       </c>
       <c r="I66" s="16">
-        <v>7.30</v>
+        <v>6.39</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3466,28 +3291,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F67" s="15">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G67" s="16">
-        <v>24836.53</v>
+        <v>49908.75</v>
       </c>
       <c r="H67" s="17">
-        <v>0.004358102184</v>
+        <v>0.0099817683453</v>
       </c>
       <c r="I67" s="16">
-        <v>7.28</v>
+        <v>6.67</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3495,28 +3320,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F68" s="15">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G68" s="16">
-        <v>24777.18</v>
+        <v>49834</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0043476879529</v>
+        <v>0.0099668183179</v>
       </c>
       <c r="I68" s="16">
-        <v>7.46</v>
+        <v>6.40</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3524,28 +3349,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F69" s="15">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G69" s="16">
-        <v>24697.75</v>
+        <v>49829.45</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0043337502548</v>
+        <v>0.0099659083162</v>
       </c>
       <c r="I69" s="16">
-        <v>7.44</v>
+        <v>6.58</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3553,28 +3378,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F70" s="15">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="G70" s="16">
-        <v>19844.78</v>
+        <v>49807.90</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0034821925228</v>
+        <v>0.0099615983083</v>
       </c>
       <c r="I70" s="16">
-        <v>7.32</v>
+        <v>6.40</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3582,28 +3407,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F71" s="15">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="G71" s="16">
-        <v>19647.34</v>
+        <v>49762.90</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0034475474377</v>
+        <v>0.0099525982917</v>
       </c>
       <c r="I71" s="16">
-        <v>7.45</v>
+        <v>6.69</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3611,28 +3436,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F72" s="15">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G72" s="16">
-        <v>17430.23</v>
+        <v>49604.90</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0030585079087</v>
+        <v>0.0099209982337</v>
       </c>
       <c r="I72" s="16">
-        <v>7.31</v>
+        <v>6.32</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3640,28 +3465,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F73" s="15">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="G73" s="16">
-        <v>17419.33</v>
+        <v>49536.85</v>
       </c>
       <c r="H73" s="17">
-        <v>0.0030565952698</v>
+        <v>0.0099073882086</v>
       </c>
       <c r="I73" s="16">
-        <v>7.35</v>
+        <v>6.32</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3669,28 +3494,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F74" s="15">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G74" s="16">
-        <v>12452.79</v>
+        <v>49240.10</v>
       </c>
       <c r="H74" s="17">
-        <v>0.0021851092441</v>
+        <v>0.0098480380996</v>
       </c>
       <c r="I74" s="16">
-        <v>7.29</v>
+        <v>6.55</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3698,28 +3523,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F75" s="15">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="G75" s="16">
-        <v>12439.29</v>
+        <v>39930.52</v>
       </c>
       <c r="H75" s="17">
-        <v>0.0021827403794</v>
+        <v>0.0079861186776</v>
       </c>
       <c r="I75" s="16">
-        <v>7.13</v>
+        <v>6.35</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
@@ -3727,28 +3552,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F76" s="15">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="G76" s="16">
-        <v>9965.88</v>
+        <v>39923</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0017487275152</v>
+        <v>0.0079846146748</v>
       </c>
       <c r="I76" s="16">
-        <v>7.35</v>
+        <v>6.40</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3756,28 +3581,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F77" s="15">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="G77" s="16">
-        <v>9962.40</v>
+        <v>39879.32</v>
       </c>
       <c r="H77" s="17">
-        <v>0.0017481168745</v>
+        <v>0.0079758786587</v>
       </c>
       <c r="I77" s="16">
-        <v>7.25</v>
+        <v>6.50</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3785,28 +3610,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F78" s="15">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="G78" s="16">
-        <v>9924.98</v>
+        <v>39858.2</v>
       </c>
       <c r="H78" s="17">
-        <v>0.0017415507325</v>
+        <v>0.007971654651</v>
       </c>
       <c r="I78" s="16">
-        <v>7.26</v>
+        <v>6.84</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3814,28 +3639,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F79" s="15">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="G79" s="16">
-        <v>9878.22</v>
+        <v>39699.24</v>
       </c>
       <c r="H79" s="17">
-        <v>0.001733345687</v>
+        <v>0.0079398625925</v>
       </c>
       <c r="I79" s="16">
-        <v>7.50</v>
+        <v>6.29</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3843,28 +3668,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F80" s="15">
-        <v>1800</v>
+        <v>8000</v>
       </c>
       <c r="G80" s="16">
-        <v>8951.92</v>
+        <v>39578.32</v>
       </c>
       <c r="H80" s="17">
-        <v>0.0015708064735</v>
+        <v>0.0079156785481</v>
       </c>
       <c r="I80" s="16">
-        <v>7.26</v>
+        <v>6.71</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3872,28 +3697,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F81" s="15">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="G81" s="16">
-        <v>7483.54</v>
+        <v>39498.28</v>
       </c>
       <c r="H81" s="17">
-        <v>0.0013131476908</v>
+        <v>0.0078996705187</v>
       </c>
       <c r="I81" s="16">
-        <v>7.30</v>
+        <v>6.53</v>
       </c>
       <c r="J81" s="11" t="s">
         <v>13</v>
@@ -3901,28 +3726,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F82" s="15">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="G82" s="16">
-        <v>7440.64</v>
+        <v>39460</v>
       </c>
       <c r="H82" s="17">
-        <v>0.0013056199652</v>
+        <v>0.0078920145046</v>
       </c>
       <c r="I82" s="16">
-        <v>7.28</v>
+        <v>6.75</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>13</v>
@@ -3930,28 +3755,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F83" s="15">
-        <v>1500</v>
+        <v>7200</v>
       </c>
       <c r="G83" s="16">
-        <v>7409.21</v>
+        <v>35929.62</v>
       </c>
       <c r="H83" s="17">
-        <v>0.0013001048972</v>
+        <v>0.0071859372069</v>
       </c>
       <c r="I83" s="16">
-        <v>7.46</v>
+        <v>6.50</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>13</v>
@@ -3959,28 +3784,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F84" s="15">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="G84" s="16">
-        <v>4997</v>
+        <v>34896.72</v>
       </c>
       <c r="H84" s="17">
-        <v>0.0008768308863</v>
+        <v>0.0069793568272</v>
       </c>
       <c r="I84" s="16">
-        <v>7.30</v>
+        <v>6.36</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>13</v>
@@ -3988,28 +3813,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F85" s="15">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="G85" s="16">
-        <v>4974.28</v>
+        <v>29955.03</v>
       </c>
       <c r="H85" s="17">
-        <v>0.0008728441747</v>
+        <v>0.0059910170108</v>
       </c>
       <c r="I85" s="16">
-        <v>7.26</v>
+        <v>6.85</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>13</v>
@@ -4017,28 +3842,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F86" s="15">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="G86" s="16">
-        <v>4966.42</v>
+        <v>29943.21</v>
       </c>
       <c r="H86" s="17">
-        <v>0.000871464969</v>
+        <v>0.0059886530064</v>
       </c>
       <c r="I86" s="16">
-        <v>7.26</v>
+        <v>6.92</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
@@ -4046,28 +3871,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F87" s="15">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="G87" s="16">
-        <v>4962.39</v>
+        <v>29942.70</v>
       </c>
       <c r="H87" s="17">
-        <v>0.0008707578191</v>
+        <v>0.0059885510063</v>
       </c>
       <c r="I87" s="16">
-        <v>7.28</v>
+        <v>6.35</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
@@ -4075,28 +3900,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F88" s="15">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="G88" s="16">
-        <v>4961.41</v>
+        <v>29941.44</v>
       </c>
       <c r="H88" s="17">
-        <v>0.000870585857</v>
+        <v>0.0059882990058</v>
       </c>
       <c r="I88" s="16">
-        <v>7.28</v>
+        <v>6.49</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
@@ -4104,7 +3929,7 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>131</v>
@@ -4113,19 +3938,19 @@
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F89" s="15">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="G89" s="16">
-        <v>4960.05</v>
+        <v>29908.23</v>
       </c>
       <c r="H89" s="17">
-        <v>0.0008703472158</v>
+        <v>0.0059816569936</v>
       </c>
       <c r="I89" s="16">
-        <v>7.35</v>
+        <v>7</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -4133,28 +3958,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F90" s="15">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="G90" s="16">
-        <v>2488.06</v>
+        <v>29898.27</v>
       </c>
       <c r="H90" s="17">
-        <v>0.0004365835211</v>
+        <v>0.0059796649899</v>
       </c>
       <c r="I90" s="16">
-        <v>7.30</v>
+        <v>6.90</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -4162,36 +3987,57 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>13</v>
+        <v>134</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F91" s="15">
+        <v>6000</v>
+      </c>
+      <c r="G91" s="16">
+        <v>29796.42</v>
+      </c>
+      <c r="H91" s="17">
+        <v>0.0059592949525</v>
+      </c>
+      <c r="I91" s="16">
+        <v>6.24</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="9">
-        <v>2505812.91</v>
-      </c>
-      <c r="H92" s="10">
-        <v>0.43969865016479986</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>13</v>
+      <c r="B92" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" s="15">
+        <v>6000</v>
+      </c>
+      <c r="G92" s="16">
+        <v>29661.06</v>
+      </c>
+      <c r="H92" s="17">
+        <v>0.0059322229027</v>
+      </c>
+      <c r="I92" s="16">
+        <v>6.23</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
@@ -4199,28 +4045,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F93" s="15">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="G93" s="16">
-        <v>148805.55</v>
+        <v>29659.62</v>
       </c>
       <c r="H93" s="17">
-        <v>0.0261111271363</v>
+        <v>0.0059319349022</v>
       </c>
       <c r="I93" s="16">
-        <v>7.33</v>
+        <v>6.16</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -4228,28 +4074,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F94" s="15">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="G94" s="16">
-        <v>148490.55</v>
+        <v>29638.47</v>
       </c>
       <c r="H94" s="17">
-        <v>0.0260558536264</v>
+        <v>0.0059277048944</v>
       </c>
       <c r="I94" s="16">
-        <v>7.28</v>
+        <v>6.65</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -4257,28 +4103,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F95" s="15">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="G95" s="16">
-        <v>99659.30</v>
+        <v>29600.22</v>
       </c>
       <c r="H95" s="17">
-        <v>0.0174873628881</v>
+        <v>0.0059200548804</v>
       </c>
       <c r="I95" s="16">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -4286,28 +4132,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F96" s="15">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="G96" s="16">
-        <v>99599.40</v>
+        <v>29565.33</v>
       </c>
       <c r="H96" s="17">
-        <v>0.0174768521476</v>
+        <v>0.0059130768675</v>
       </c>
       <c r="I96" s="16">
-        <v>7.34</v>
+        <v>6.24</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -4315,28 +4161,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F97" s="15">
-        <v>15000</v>
+        <v>5500</v>
       </c>
       <c r="G97" s="16">
-        <v>74848.58</v>
+        <v>27448.11</v>
       </c>
       <c r="H97" s="17">
-        <v>0.0131337896224</v>
+        <v>0.0054896320893</v>
       </c>
       <c r="I97" s="16">
-        <v>7.38</v>
+        <v>6.90</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4344,28 +4190,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F98" s="15">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="G98" s="16">
-        <v>74318.63</v>
+        <v>24793.33</v>
       </c>
       <c r="H98" s="17">
-        <v>0.0130407985221</v>
+        <v>0.0049586751135</v>
       </c>
       <c r="I98" s="16">
-        <v>7.28</v>
+        <v>6.62</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4373,28 +4219,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D99" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F99" s="15">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G99" s="16">
-        <v>49868.55</v>
+        <v>24760.83</v>
       </c>
       <c r="H99" s="17">
-        <v>0.0087505072838</v>
+        <v>0.0049521751015</v>
       </c>
       <c r="I99" s="16">
-        <v>7.40</v>
+        <v>6.65</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4402,28 +4248,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D100" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F100" s="15">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="G100" s="16">
-        <v>49830.60</v>
+        <v>22455.74</v>
       </c>
       <c r="H100" s="17">
-        <v>0.0087438481419</v>
+        <v>0.0044911562542</v>
       </c>
       <c r="I100" s="16">
-        <v>7.30</v>
+        <v>6.54</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4431,28 +4277,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D101" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F101" s="15">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="G101" s="16">
-        <v>49807.40</v>
+        <v>22449.31</v>
       </c>
       <c r="H101" s="17">
-        <v>0.008739777204</v>
+        <v>0.0044898702518</v>
       </c>
       <c r="I101" s="16">
-        <v>7.43</v>
+        <v>6.87</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4460,28 +4306,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F102" s="15">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G102" s="16">
-        <v>49615.65</v>
+        <v>19985.18</v>
       </c>
       <c r="H102" s="17">
-        <v>0.0087061305515</v>
+        <v>0.0039970433461</v>
       </c>
       <c r="I102" s="16">
-        <v>7.25</v>
+        <v>6.78</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4489,28 +4335,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F103" s="15">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G103" s="16">
-        <v>49495.20</v>
+        <v>19969.80</v>
       </c>
       <c r="H103" s="17">
-        <v>0.0086849950142</v>
+        <v>0.0039939673404</v>
       </c>
       <c r="I103" s="16">
-        <v>7.30</v>
+        <v>6.90</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4518,28 +4364,28 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="12" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F104" s="15">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G104" s="16">
-        <v>49131.80</v>
+        <v>19940</v>
       </c>
       <c r="H104" s="17">
-        <v>0.0086212286856</v>
+        <v>0.0039880073295</v>
       </c>
       <c r="I104" s="16">
-        <v>7.50</v>
+        <v>6.87</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4547,28 +4393,28 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F105" s="15">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="G105" s="16">
-        <v>44954.60</v>
+        <v>19935</v>
       </c>
       <c r="H105" s="17">
-        <v>0.0078882493022</v>
+        <v>0.0039870073276</v>
       </c>
       <c r="I105" s="16">
-        <v>7.38</v>
+        <v>7</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4576,28 +4422,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F106" s="15">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="G106" s="16">
-        <v>44577</v>
+        <v>19931.48</v>
       </c>
       <c r="H106" s="17">
-        <v>0.0078219912789</v>
+        <v>0.0039863033263</v>
       </c>
       <c r="I106" s="16">
-        <v>7.70</v>
+        <v>6.61</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4605,28 +4451,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>42</v>
+        <v>158</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F107" s="15">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G107" s="16">
-        <v>34761.55</v>
+        <v>19929.04</v>
       </c>
       <c r="H107" s="17">
-        <v>0.0060996599354</v>
+        <v>0.0039858153254</v>
       </c>
       <c r="I107" s="16">
-        <v>7.37</v>
+        <v>6.84</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
@@ -4634,28 +4480,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F108" s="15">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G108" s="16">
-        <v>34758.12</v>
+        <v>19928.78</v>
       </c>
       <c r="H108" s="17">
-        <v>0.0060990580683</v>
+        <v>0.0039857633253</v>
       </c>
       <c r="I108" s="16">
-        <v>7.70</v>
+        <v>6.87</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4663,28 +4509,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F109" s="15">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G109" s="16">
-        <v>34729.03</v>
+        <v>19914.30</v>
       </c>
       <c r="H109" s="17">
-        <v>0.0060939536035</v>
+        <v>0.00398286732</v>
       </c>
       <c r="I109" s="16">
-        <v>7.70</v>
+        <v>6.83</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
@@ -4692,28 +4538,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F110" s="15">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G110" s="16">
-        <v>34725.78</v>
+        <v>19914.18</v>
       </c>
       <c r="H110" s="17">
-        <v>0.0060933833213</v>
+        <v>0.00398284332</v>
       </c>
       <c r="I110" s="16">
-        <v>7.79</v>
+        <v>6.84</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>13</v>
@@ -4721,28 +4567,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D111" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F111" s="15">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G111" s="16">
-        <v>34651.86</v>
+        <v>19908.1</v>
       </c>
       <c r="H111" s="17">
-        <v>0.0060804124709</v>
+        <v>0.0039816273177</v>
       </c>
       <c r="I111" s="16">
-        <v>7.64</v>
+        <v>6.48</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
@@ -4750,28 +4596,28 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
       <c r="B112" s="12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D112" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F112" s="15">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G112" s="16">
-        <v>29843.01</v>
+        <v>19756.30</v>
       </c>
       <c r="H112" s="17">
-        <v>0.0052365965398</v>
+        <v>0.0039512672619</v>
       </c>
       <c r="I112" s="16">
-        <v>7.39</v>
+        <v>6.72</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
@@ -4779,28 +4625,28 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F113" s="15">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G113" s="16">
-        <v>29821.68</v>
+        <v>19752.20</v>
       </c>
       <c r="H113" s="17">
-        <v>0.0052328537336</v>
+        <v>0.0039504472604</v>
       </c>
       <c r="I113" s="16">
-        <v>7.28</v>
+        <v>7.05</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
@@ -4808,28 +4654,28 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F114" s="15">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G114" s="16">
-        <v>29794.20</v>
+        <v>19738.86</v>
       </c>
       <c r="H114" s="17">
-        <v>0.0052280317778</v>
+        <v>0.0039477792555</v>
       </c>
       <c r="I114" s="16">
-        <v>7.64</v>
+        <v>6.62</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
@@ -4837,28 +4683,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F115" s="15">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G115" s="16">
-        <v>29717.97</v>
+        <v>19725.96</v>
       </c>
       <c r="H115" s="17">
-        <v>0.0052146555884</v>
+        <v>0.0039451992508</v>
       </c>
       <c r="I115" s="16">
-        <v>7.70</v>
+        <v>6.85</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
@@ -4866,28 +4712,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F116" s="15">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G116" s="16">
-        <v>29698.29</v>
+        <v>19716.08</v>
       </c>
       <c r="H116" s="17">
-        <v>0.0052112023101</v>
+        <v>0.0039432232472</v>
       </c>
       <c r="I116" s="16">
-        <v>7.89</v>
+        <v>6.57</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
@@ -4895,28 +4741,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F117" s="15">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="G117" s="16">
-        <v>27230.12</v>
+        <v>17256.12</v>
       </c>
       <c r="H117" s="17">
-        <v>0.0047781089163</v>
+        <v>0.0034512303429</v>
       </c>
       <c r="I117" s="16">
-        <v>7.70</v>
+        <v>6.53</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4924,28 +4770,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D118" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F118" s="15">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G118" s="16">
-        <v>24900.40</v>
+        <v>17250.03</v>
       </c>
       <c r="H118" s="17">
-        <v>0.0043693095462</v>
+        <v>0.0034500123407</v>
       </c>
       <c r="I118" s="16">
-        <v>7.30</v>
+        <v>6.53</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
@@ -4953,28 +4799,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F119" s="15">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G119" s="16">
-        <v>24873.88</v>
+        <v>17214.26</v>
       </c>
       <c r="H119" s="17">
-        <v>0.004364656043</v>
+        <v>0.0034428583275</v>
       </c>
       <c r="I119" s="16">
-        <v>7.71</v>
+        <v>7.05</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
@@ -4982,28 +4828,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F120" s="15">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G120" s="16">
-        <v>24837.63</v>
+        <v>14960.07</v>
       </c>
       <c r="H120" s="17">
-        <v>0.0043582952026</v>
+        <v>0.002992019499</v>
       </c>
       <c r="I120" s="16">
-        <v>7.70</v>
+        <v>6.50</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>13</v>
@@ -5011,28 +4857,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F121" s="15">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G121" s="16">
-        <v>24793.65</v>
+        <v>14955.42</v>
       </c>
       <c r="H121" s="17">
-        <v>0.0043505779678</v>
+        <v>0.0029910894972</v>
       </c>
       <c r="I121" s="16">
-        <v>7.79</v>
+        <v>6.80</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -5040,28 +4886,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D122" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F122" s="15">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G122" s="16">
-        <v>24781.33</v>
+        <v>14953.86</v>
       </c>
       <c r="H122" s="17">
-        <v>0.0043484161594</v>
+        <v>0.0029907774967</v>
       </c>
       <c r="I122" s="16">
-        <v>7.32</v>
+        <v>7.04</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
@@ -5069,28 +4915,28 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F123" s="15">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G123" s="16">
-        <v>24754.63</v>
+        <v>14800.61</v>
       </c>
       <c r="H123" s="17">
-        <v>0.0043437310714</v>
+        <v>0.0029601274403</v>
       </c>
       <c r="I123" s="16">
-        <v>7.70</v>
+        <v>6.65</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
@@ -5101,25 +4947,25 @@
         <v>107</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F124" s="15">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G124" s="16">
-        <v>24620.58</v>
+        <v>14800.59</v>
       </c>
       <c r="H124" s="17">
-        <v>0.0043202091222</v>
+        <v>0.0029601234403</v>
       </c>
       <c r="I124" s="16">
-        <v>7.50</v>
+        <v>6.23</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
@@ -5127,28 +4973,28 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D125" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F125" s="15">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G125" s="16">
-        <v>24606.15</v>
+        <v>14799.96</v>
       </c>
       <c r="H125" s="17">
-        <v>0.004317677069</v>
+        <v>0.0029599974401</v>
       </c>
       <c r="I125" s="16">
-        <v>7.90</v>
+        <v>6.33</v>
       </c>
       <c r="J125" s="11" t="s">
         <v>13</v>
@@ -5156,28 +5002,28 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F126" s="15">
-        <v>5000</v>
+        <v>2800</v>
       </c>
       <c r="G126" s="16">
-        <v>24600.90</v>
+        <v>13816.53</v>
       </c>
       <c r="H126" s="17">
-        <v>0.0043167558439</v>
+        <v>0.0027633110786</v>
       </c>
       <c r="I126" s="16">
-        <v>7.90</v>
+        <v>6.55</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>13</v>
@@ -5185,28 +5031,28 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
       <c r="B127" s="12" t="s">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F127" s="15">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G127" s="16">
-        <v>24571.43</v>
+        <v>12464.99</v>
       </c>
       <c r="H127" s="17">
-        <v>0.0043115846999</v>
+        <v>0.0024930025818</v>
       </c>
       <c r="I127" s="16">
-        <v>7.86</v>
+        <v>6.84</v>
       </c>
       <c r="J127" s="11" t="s">
         <v>13</v>
@@ -5214,28 +5060,28 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
       <c r="B128" s="12" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D128" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F128" s="15">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="G128" s="16">
-        <v>22379.15</v>
+        <v>12457.80</v>
       </c>
       <c r="H128" s="17">
-        <v>0.0039269021273</v>
+        <v>0.0024915645792</v>
       </c>
       <c r="I128" s="16">
-        <v>7.30</v>
+        <v>6.87</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>13</v>
@@ -5243,28 +5089,28 @@
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
       <c r="B129" s="12" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D129" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F129" s="15">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="G129" s="16">
-        <v>22143.06</v>
+        <v>12332.60</v>
       </c>
       <c r="H129" s="17">
-        <v>0.0038854750703</v>
+        <v>0.0024665245332</v>
       </c>
       <c r="I129" s="16">
-        <v>7.85</v>
+        <v>6.70</v>
       </c>
       <c r="J129" s="11" t="s">
         <v>13</v>
@@ -5272,28 +5118,28 @@
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
       <c r="B130" s="12" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F130" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G130" s="16">
-        <v>19975.76</v>
+        <v>9994.65</v>
       </c>
       <c r="H130" s="17">
-        <v>0.0035051757747</v>
+        <v>0.0019989336738</v>
       </c>
       <c r="I130" s="16">
-        <v>7.38</v>
+        <v>6.52</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>13</v>
@@ -5301,28 +5147,28 @@
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1">
       <c r="B131" s="12" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F131" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G131" s="16">
-        <v>19974.62</v>
+        <v>9983.07</v>
       </c>
       <c r="H131" s="17">
-        <v>0.0035049757372</v>
+        <v>0.0019966176695</v>
       </c>
       <c r="I131" s="16">
-        <v>7.74</v>
+        <v>6.88</v>
       </c>
       <c r="J131" s="11" t="s">
         <v>13</v>
@@ -5330,28 +5176,28 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
       <c r="B132" s="12" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D132" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F132" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G132" s="16">
-        <v>19947.16</v>
+        <v>9977.50</v>
       </c>
       <c r="H132" s="17">
-        <v>0.0035001572909</v>
+        <v>0.0019955036675</v>
       </c>
       <c r="I132" s="16">
-        <v>7.44</v>
+        <v>6.86</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>13</v>
@@ -5359,28 +5205,28 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
       <c r="B133" s="12" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F133" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G133" s="16">
-        <v>19925.86</v>
+        <v>9967.68</v>
       </c>
       <c r="H133" s="17">
-        <v>0.0034964197488</v>
+        <v>0.0019935396639</v>
       </c>
       <c r="I133" s="16">
-        <v>7.99</v>
+        <v>6.58</v>
       </c>
       <c r="J133" s="11" t="s">
         <v>13</v>
@@ -5388,28 +5234,28 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
       <c r="B134" s="12" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D134" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F134" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G134" s="16">
-        <v>19913.74</v>
+        <v>9966.46</v>
       </c>
       <c r="H134" s="17">
-        <v>0.0034942930347</v>
+        <v>0.0019932956634</v>
       </c>
       <c r="I134" s="16">
-        <v>7.91</v>
+        <v>6.83</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>13</v>
@@ -5417,28 +5263,28 @@
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1">
       <c r="B135" s="12" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D135" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F135" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G135" s="16">
-        <v>19832.70</v>
+        <v>9963.49</v>
       </c>
       <c r="H135" s="17">
-        <v>0.0034800728276</v>
+        <v>0.0019927016623</v>
       </c>
       <c r="I135" s="16">
-        <v>7.70</v>
+        <v>7.04</v>
       </c>
       <c r="J135" s="11" t="s">
         <v>13</v>
@@ -5446,28 +5292,28 @@
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1">
       <c r="B136" s="12" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D136" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F136" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G136" s="16">
-        <v>19817.48</v>
+        <v>9963.49</v>
       </c>
       <c r="H136" s="17">
-        <v>0.003477402152</v>
+        <v>0.0019927016623</v>
       </c>
       <c r="I136" s="16">
-        <v>7.64</v>
+        <v>7.04</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>13</v>
@@ -5475,28 +5321,28 @@
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1">
       <c r="B137" s="12" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F137" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G137" s="16">
-        <v>19811.98</v>
+        <v>9958.90</v>
       </c>
       <c r="H137" s="17">
-        <v>0.0034764370589</v>
+        <v>0.0019917836606</v>
       </c>
       <c r="I137" s="16">
-        <v>7.37</v>
+        <v>6.55</v>
       </c>
       <c r="J137" s="11" t="s">
         <v>13</v>
@@ -5504,28 +5350,28 @@
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1">
       <c r="B138" s="12" t="s">
-        <v>199</v>
+        <v>123</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F138" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G138" s="16">
-        <v>19805.04</v>
+        <v>9958.88</v>
       </c>
       <c r="H138" s="17">
-        <v>0.003475219287</v>
+        <v>0.0019917796606</v>
       </c>
       <c r="I138" s="16">
-        <v>7.99</v>
+        <v>6.85</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>13</v>
@@ -5536,25 +5382,25 @@
         <v>201</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D139" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F139" s="15">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G139" s="16">
-        <v>19604.34</v>
+        <v>9955.83</v>
       </c>
       <c r="H139" s="17">
-        <v>0.003440002165</v>
+        <v>0.0019911696595</v>
       </c>
       <c r="I139" s="16">
-        <v>8.19</v>
+        <v>7.04</v>
       </c>
       <c r="J139" s="11" t="s">
         <v>13</v>
@@ -5562,28 +5408,28 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
       <c r="B140" s="12" t="s">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D140" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F140" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G140" s="16">
-        <v>14981.69</v>
+        <v>9910.84</v>
       </c>
       <c r="H140" s="17">
-        <v>0.0026288590197</v>
+        <v>0.001982171643</v>
       </c>
       <c r="I140" s="16">
-        <v>7.44</v>
+        <v>6.32</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>13</v>
@@ -5591,28 +5437,28 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1">
       <c r="B141" s="12" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D141" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F141" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G141" s="16">
-        <v>14968.23</v>
+        <v>9888.88</v>
       </c>
       <c r="H141" s="17">
-        <v>0.0026264971739</v>
+        <v>0.0019777796349</v>
       </c>
       <c r="I141" s="16">
-        <v>7.75</v>
+        <v>6.31</v>
       </c>
       <c r="J141" s="11" t="s">
         <v>13</v>
@@ -5620,28 +5466,28 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
       <c r="B142" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D142" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F142" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G142" s="16">
-        <v>14929.83</v>
+        <v>9885.05</v>
       </c>
       <c r="H142" s="17">
-        <v>0.0026197590698</v>
+        <v>0.0019770136335</v>
       </c>
       <c r="I142" s="16">
-        <v>7.46</v>
+        <v>6.34</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>13</v>
@@ -5649,28 +5495,28 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1">
       <c r="B143" s="12" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D143" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F143" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G143" s="16">
-        <v>14919.11</v>
+        <v>9877.54</v>
       </c>
       <c r="H143" s="17">
-        <v>0.0026178780157</v>
+        <v>0.0019755116307</v>
       </c>
       <c r="I143" s="16">
-        <v>7.33</v>
+        <v>6.66</v>
       </c>
       <c r="J143" s="11" t="s">
         <v>13</v>
@@ -5678,28 +5524,28 @@
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1">
       <c r="B144" s="12" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D144" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F144" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G144" s="16">
-        <v>14918.04</v>
+        <v>9877.52</v>
       </c>
       <c r="H144" s="17">
-        <v>0.0026176902613</v>
+        <v>0.0019755076307</v>
       </c>
       <c r="I144" s="16">
-        <v>7.71</v>
+        <v>6.20</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>13</v>
@@ -5707,28 +5553,28 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1">
       <c r="B145" s="12" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D145" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F145" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G145" s="16">
-        <v>14915.18</v>
+        <v>9876.10</v>
       </c>
       <c r="H145" s="17">
-        <v>0.0026171884129</v>
+        <v>0.0019752236302</v>
       </c>
       <c r="I145" s="16">
-        <v>7.99</v>
+        <v>7.05</v>
       </c>
       <c r="J145" s="11" t="s">
         <v>13</v>
@@ -5736,28 +5582,28 @@
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1">
       <c r="B146" s="12" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D146" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F146" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G146" s="16">
-        <v>14893.22</v>
+        <v>9872.21</v>
       </c>
       <c r="H146" s="17">
-        <v>0.0026133350596</v>
+        <v>0.0019744456288</v>
       </c>
       <c r="I146" s="16">
-        <v>7.70</v>
+        <v>6.39</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>13</v>
@@ -5765,28 +5611,28 @@
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1">
       <c r="B147" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D147" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F147" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G147" s="16">
-        <v>14877.80</v>
+        <v>9858.85</v>
       </c>
       <c r="H147" s="17">
-        <v>0.0026106292897</v>
+        <v>0.0019717736239</v>
       </c>
       <c r="I147" s="16">
-        <v>7.89</v>
+        <v>6.62</v>
       </c>
       <c r="J147" s="11" t="s">
         <v>13</v>
@@ -5794,28 +5640,28 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1">
       <c r="B148" s="12" t="s">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D148" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F148" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G148" s="16">
-        <v>14874.81</v>
+        <v>9857.83</v>
       </c>
       <c r="H148" s="17">
-        <v>0.00261010463</v>
+        <v>0.0019715696235</v>
       </c>
       <c r="I148" s="16">
-        <v>7.68</v>
+        <v>6.58</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>13</v>
@@ -5823,28 +5669,28 @@
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1">
       <c r="B149" s="12" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D149" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F149" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G149" s="16">
-        <v>14869.16</v>
+        <v>9857.06</v>
       </c>
       <c r="H149" s="17">
-        <v>0.0026091132163</v>
+        <v>0.0019714156232</v>
       </c>
       <c r="I149" s="16">
-        <v>7.30</v>
+        <v>6.70</v>
       </c>
       <c r="J149" s="11" t="s">
         <v>13</v>
@@ -5852,28 +5698,28 @@
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1">
       <c r="B150" s="12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D150" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F150" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G150" s="16">
-        <v>14837.03</v>
+        <v>9855.28</v>
       </c>
       <c r="H150" s="17">
-        <v>0.0026034753183</v>
+        <v>0.0019710596225</v>
       </c>
       <c r="I150" s="16">
-        <v>7.57</v>
+        <v>6.70</v>
       </c>
       <c r="J150" s="11" t="s">
         <v>13</v>
@@ -5881,28 +5727,28 @@
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1">
       <c r="B151" s="12" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D151" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F151" s="15">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G151" s="16">
-        <v>14744.85</v>
+        <v>9853.57</v>
       </c>
       <c r="H151" s="17">
-        <v>0.0025873003591</v>
+        <v>0.0019707176219</v>
       </c>
       <c r="I151" s="16">
-        <v>7.90</v>
+        <v>6.62</v>
       </c>
       <c r="J151" s="11" t="s">
         <v>13</v>
@@ -5910,28 +5756,28 @@
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
       <c r="B152" s="12" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D152" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F152" s="15">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G152" s="16">
-        <v>14735.30</v>
+        <v>7474.75</v>
       </c>
       <c r="H152" s="17">
-        <v>0.0025856246066</v>
+        <v>0.0014949527475</v>
       </c>
       <c r="I152" s="16">
-        <v>7.90</v>
+        <v>6.85</v>
       </c>
       <c r="J152" s="11" t="s">
         <v>13</v>
@@ -5939,28 +5785,28 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1">
       <c r="B153" s="12" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D153" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F153" s="15">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G153" s="16">
-        <v>14714.91</v>
+        <v>7402.23</v>
       </c>
       <c r="H153" s="17">
-        <v>0.0025820467436</v>
+        <v>0.0014804487209</v>
       </c>
       <c r="I153" s="16">
-        <v>8.52</v>
+        <v>6.51</v>
       </c>
       <c r="J153" s="11" t="s">
         <v>13</v>
@@ -5968,28 +5814,28 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1">
       <c r="B154" s="12" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D154" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F154" s="15">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="G154" s="16">
-        <v>12494.78</v>
+        <v>7393.74</v>
       </c>
       <c r="H154" s="17">
-        <v>0.0021924772908</v>
+        <v>0.0014787507177</v>
       </c>
       <c r="I154" s="16">
-        <v>7.63</v>
+        <v>6.64</v>
       </c>
       <c r="J154" s="11" t="s">
         <v>13</v>
@@ -5997,28 +5843,28 @@
     </row>
     <row r="155" spans="2:10" ht="15" customHeight="1">
       <c r="B155" s="12" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D155" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F155" s="15">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="G155" s="16">
-        <v>12459.29</v>
+        <v>6893.57</v>
       </c>
       <c r="H155" s="17">
-        <v>0.0021862498086</v>
+        <v>0.0013787165339</v>
       </c>
       <c r="I155" s="16">
-        <v>7.46</v>
+        <v>6.63</v>
       </c>
       <c r="J155" s="11" t="s">
         <v>13</v>
@@ -6026,28 +5872,28 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1">
       <c r="B156" s="12" t="s">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F156" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G156" s="16">
-        <v>9993.50</v>
+        <v>4995.67</v>
       </c>
       <c r="H156" s="17">
-        <v>0.0017535740369</v>
+        <v>0.0009991358363</v>
       </c>
       <c r="I156" s="16">
-        <v>7.91</v>
+        <v>6.34</v>
       </c>
       <c r="J156" s="11" t="s">
         <v>13</v>
@@ -6055,28 +5901,28 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1">
       <c r="B157" s="12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D157" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F157" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G157" s="16">
-        <v>9991.65</v>
+        <v>4991.42</v>
       </c>
       <c r="H157" s="17">
-        <v>0.0017532494147</v>
+        <v>0.0009982858347</v>
       </c>
       <c r="I157" s="16">
-        <v>7.63</v>
+        <v>6.97</v>
       </c>
       <c r="J157" s="11" t="s">
         <v>13</v>
@@ -6084,28 +5930,28 @@
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1">
       <c r="B158" s="12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D158" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E158" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F158" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G158" s="16">
-        <v>9987.59</v>
+        <v>4989.74</v>
       </c>
       <c r="H158" s="17">
-        <v>0.0017525370006</v>
+        <v>0.0009979498341</v>
       </c>
       <c r="I158" s="16">
-        <v>7.56</v>
+        <v>6.83</v>
       </c>
       <c r="J158" s="11" t="s">
         <v>13</v>
@@ -6113,28 +5959,28 @@
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1">
       <c r="B159" s="12" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C159" s="13" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D159" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E159" s="13" t="s">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="F159" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G159" s="16">
-        <v>9981.18</v>
+        <v>4983.23</v>
       </c>
       <c r="H159" s="17">
-        <v>0.0017514122285</v>
+        <v>0.0009966478317</v>
       </c>
       <c r="I159" s="16">
-        <v>7.65</v>
+        <v>6.83</v>
       </c>
       <c r="J159" s="11" t="s">
         <v>13</v>
@@ -6142,28 +5988,28 @@
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1">
       <c r="B160" s="12" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D160" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F160" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G160" s="16">
-        <v>9980.93</v>
+        <v>4983</v>
       </c>
       <c r="H160" s="17">
-        <v>0.0017513683607</v>
+        <v>0.0009966018316</v>
       </c>
       <c r="I160" s="16">
-        <v>7.75</v>
+        <v>6.92</v>
       </c>
       <c r="J160" s="11" t="s">
         <v>13</v>
@@ -6171,28 +6017,28 @@
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1">
       <c r="B161" s="12" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D161" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F161" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G161" s="16">
-        <v>9977.63</v>
+        <v>4979.22</v>
       </c>
       <c r="H161" s="17">
-        <v>0.0017507893048</v>
+        <v>0.0009958458302</v>
       </c>
       <c r="I161" s="16">
-        <v>7.44</v>
+        <v>6.63</v>
       </c>
       <c r="J161" s="11" t="s">
         <v>13</v>
@@ -6200,28 +6046,28 @@
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
       <c r="B162" s="12" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C162" s="13" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D162" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F162" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G162" s="16">
-        <v>9976.7</v>
+        <v>4978.32</v>
       </c>
       <c r="H162" s="17">
-        <v>0.0017506261164</v>
+        <v>0.0009956658299</v>
       </c>
       <c r="I162" s="16">
-        <v>7.75</v>
+        <v>6.63</v>
       </c>
       <c r="J162" s="11" t="s">
         <v>13</v>
@@ -6229,28 +6075,28 @@
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1">
       <c r="B163" s="12" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D163" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="F163" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G163" s="16">
-        <v>9974.91</v>
+        <v>4977.92</v>
       </c>
       <c r="H163" s="17">
-        <v>0.0017503120225</v>
+        <v>0.0009955858297</v>
       </c>
       <c r="I163" s="16">
-        <v>7.65</v>
+        <v>7.04</v>
       </c>
       <c r="J163" s="11" t="s">
         <v>13</v>
@@ -6258,28 +6104,28 @@
     </row>
     <row r="164" spans="2:10" ht="15" customHeight="1">
       <c r="B164" s="12" t="s">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D164" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F164" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G164" s="16">
-        <v>9974.90</v>
+        <v>4977.42</v>
       </c>
       <c r="H164" s="17">
-        <v>0.0017503102678</v>
+        <v>0.0009954858295</v>
       </c>
       <c r="I164" s="16">
-        <v>7.66</v>
+        <v>6.63</v>
       </c>
       <c r="J164" s="11" t="s">
         <v>13</v>
@@ -6287,28 +6133,28 @@
     </row>
     <row r="165" spans="2:10" ht="15" customHeight="1">
       <c r="B165" s="12" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C165" s="13" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D165" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F165" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G165" s="16">
-        <v>9963.27</v>
+        <v>4942.64</v>
       </c>
       <c r="H165" s="17">
-        <v>0.0017482695347</v>
+        <v>0.0009885298168</v>
       </c>
       <c r="I165" s="16">
-        <v>7.92</v>
+        <v>6.23</v>
       </c>
       <c r="J165" s="11" t="s">
         <v>13</v>
@@ -6316,28 +6162,28 @@
     </row>
     <row r="166" spans="2:10" ht="15" customHeight="1">
       <c r="B166" s="12" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D166" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F166" s="15">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G166" s="16">
-        <v>9961.11</v>
+        <v>4927.6</v>
       </c>
       <c r="H166" s="17">
-        <v>0.0017478905163</v>
+        <v>0.0009855218112</v>
       </c>
       <c r="I166" s="16">
-        <v>7.50</v>
+        <v>6.31</v>
       </c>
       <c r="J166" s="11" t="s">
         <v>13</v>
@@ -6345,28 +6191,28 @@
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1">
       <c r="B167" s="12" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="C167" s="13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D167" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E167" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F167" s="15">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G167" s="16">
-        <v>9957.92</v>
+        <v>2498.26</v>
       </c>
       <c r="H167" s="17">
-        <v>0.0017473307624</v>
+        <v>0.0004996529183</v>
       </c>
       <c r="I167" s="16">
-        <v>7.71</v>
+        <v>6.37</v>
       </c>
       <c r="J167" s="11" t="s">
         <v>13</v>
@@ -6374,28 +6220,28 @@
     </row>
     <row r="168" spans="2:10" ht="15" customHeight="1">
       <c r="B168" s="12" t="s">
-        <v>224</v>
+        <v>76</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D168" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E168" s="13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="F168" s="15">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G168" s="16">
-        <v>9953.24</v>
+        <v>2496.50</v>
       </c>
       <c r="H168" s="17">
-        <v>0.0017465095559</v>
+        <v>0.0004993009176</v>
       </c>
       <c r="I168" s="16">
-        <v>7.46</v>
+        <v>6.40</v>
       </c>
       <c r="J168" s="11" t="s">
         <v>13</v>
@@ -6403,28 +6249,28 @@
     </row>
     <row r="169" spans="2:10" ht="15" customHeight="1">
       <c r="B169" s="12" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D169" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E169" s="13" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F169" s="15">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G169" s="16">
-        <v>9947.18</v>
+        <v>2488.26</v>
       </c>
       <c r="H169" s="17">
-        <v>0.0017454461989</v>
+        <v>0.0004976529146</v>
       </c>
       <c r="I169" s="16">
-        <v>7.46</v>
+        <v>6.63</v>
       </c>
       <c r="J169" s="11" t="s">
         <v>13</v>
@@ -6432,57 +6278,36 @@
     </row>
     <row r="170" spans="2:10" ht="15" customHeight="1">
       <c r="B170" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C170" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E170" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F170" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G170" s="16">
-        <v>9939.18</v>
-      </c>
-      <c r="H170" s="17">
-        <v>0.0017440424272</v>
-      </c>
-      <c r="I170" s="16">
-        <v>7.45</v>
+        <v>13</v>
       </c>
       <c r="J170" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="171" spans="2:10" ht="15" customHeight="1">
-      <c r="B171" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C171" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="D171" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F171" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G171" s="16">
-        <v>9936.92</v>
-      </c>
-      <c r="H171" s="17">
-        <v>0.0017436458617</v>
-      </c>
-      <c r="I171" s="16">
-        <v>7.48</v>
+      <c r="B171" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J171" s="11" t="s">
         <v>13</v>
@@ -6490,57 +6315,36 @@
     </row>
     <row r="172" spans="2:10" ht="15" customHeight="1">
       <c r="B172" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C172" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E172" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F172" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G172" s="16">
-        <v>9933.46</v>
-      </c>
-      <c r="H172" s="17">
-        <v>0.0017430387305</v>
-      </c>
-      <c r="I172" s="16">
-        <v>7.64</v>
+        <v>13</v>
       </c>
       <c r="J172" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="173" spans="2:10" ht="15" customHeight="1">
-      <c r="B173" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C173" s="13" t="s">
+      <c r="B173" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="D173" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E173" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F173" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G173" s="16">
-        <v>9931.43</v>
-      </c>
-      <c r="H173" s="17">
-        <v>0.0017426825234</v>
-      </c>
-      <c r="I173" s="16">
-        <v>7.88</v>
+      <c r="C173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G173" s="9">
+        <v>927667.9900000001</v>
+      </c>
+      <c r="H173" s="10">
+        <v>0.1855339389903</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J173" s="11" t="s">
         <v>13</v>
@@ -6548,28 +6352,28 @@
     </row>
     <row r="174" spans="2:10" ht="15" customHeight="1">
       <c r="B174" s="12" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D174" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E174" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F174" s="15">
-        <v>2000</v>
+        <v>320000000</v>
       </c>
       <c r="G174" s="16">
-        <v>9930.03</v>
+        <v>316072</v>
       </c>
       <c r="H174" s="17">
-        <v>0.0017424368633</v>
+        <v>0.0632145161813</v>
       </c>
       <c r="I174" s="16">
-        <v>7.57</v>
+        <v>5.60</v>
       </c>
       <c r="J174" s="11" t="s">
         <v>13</v>
@@ -6577,28 +6381,28 @@
     </row>
     <row r="175" spans="2:10" ht="15" customHeight="1">
       <c r="B175" s="12" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D175" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F175" s="15">
-        <v>2000</v>
+        <v>215000000</v>
       </c>
       <c r="G175" s="16">
-        <v>9919.88</v>
+        <v>214386.82</v>
       </c>
       <c r="H175" s="17">
-        <v>0.001740655828</v>
+        <v>0.042877442804</v>
       </c>
       <c r="I175" s="16">
-        <v>7.37</v>
+        <v>5.80</v>
       </c>
       <c r="J175" s="11" t="s">
         <v>13</v>
@@ -6606,28 +6410,28 @@
     </row>
     <row r="176" spans="2:10" ht="15" customHeight="1">
       <c r="B176" s="12" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D176" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E176" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F176" s="15">
-        <v>2000</v>
+        <v>120000000</v>
       </c>
       <c r="G176" s="16">
-        <v>9918.42</v>
+        <v>119268</v>
       </c>
       <c r="H176" s="17">
-        <v>0.0017403996397</v>
+        <v>0.0238536438403</v>
       </c>
       <c r="I176" s="16">
-        <v>7.70</v>
+        <v>5.60</v>
       </c>
       <c r="J176" s="11" t="s">
         <v>13</v>
@@ -6635,28 +6439,28 @@
     </row>
     <row r="177" spans="2:10" ht="15" customHeight="1">
       <c r="B177" s="12" t="s">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="C177" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D177" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E177" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F177" s="15">
-        <v>2000</v>
+        <v>75500000</v>
       </c>
       <c r="G177" s="16">
-        <v>9915.36</v>
+        <v>74799.89</v>
       </c>
       <c r="H177" s="17">
-        <v>0.001739862697</v>
+        <v>0.0149600054948</v>
       </c>
       <c r="I177" s="16">
-        <v>7.79</v>
+        <v>5.60</v>
       </c>
       <c r="J177" s="11" t="s">
         <v>13</v>
@@ -6664,7 +6468,7 @@
     </row>
     <row r="178" spans="2:10" ht="15" customHeight="1">
       <c r="B178" s="12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C178" s="13" t="s">
         <v>259</v>
@@ -6673,19 +6477,19 @@
         <v>13</v>
       </c>
       <c r="E178" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F178" s="15">
-        <v>2000</v>
+        <v>46500000</v>
       </c>
       <c r="G178" s="16">
-        <v>9911.58</v>
+        <v>46173.43</v>
       </c>
       <c r="H178" s="17">
-        <v>0.0017391994149</v>
+        <v>0.0092347029723</v>
       </c>
       <c r="I178" s="16">
-        <v>7.40</v>
+        <v>5.61</v>
       </c>
       <c r="J178" s="11" t="s">
         <v>13</v>
@@ -6693,28 +6497,28 @@
     </row>
     <row r="179" spans="2:10" ht="15" customHeight="1">
       <c r="B179" s="12" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C179" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D179" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E179" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F179" s="15">
-        <v>2000</v>
+        <v>41000000</v>
       </c>
       <c r="G179" s="16">
-        <v>9906.2</v>
+        <v>40625.18</v>
       </c>
       <c r="H179" s="17">
-        <v>0.0017382553784</v>
+        <v>0.0081250509329</v>
       </c>
       <c r="I179" s="16">
-        <v>7.68</v>
+        <v>5.61</v>
       </c>
       <c r="J179" s="11" t="s">
         <v>13</v>
@@ -6722,28 +6526,28 @@
     </row>
     <row r="180" spans="2:10" ht="15" customHeight="1">
       <c r="B180" s="12" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D180" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E180" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F180" s="15">
-        <v>2000</v>
+        <v>38157600</v>
       </c>
       <c r="G180" s="16">
-        <v>9898.42</v>
+        <v>37768.47</v>
       </c>
       <c r="H180" s="17">
-        <v>0.0017368902105</v>
+        <v>0.0075537078828</v>
       </c>
       <c r="I180" s="16">
-        <v>7.97</v>
+        <v>5.61</v>
       </c>
       <c r="J180" s="11" t="s">
         <v>13</v>
@@ -6751,28 +6555,28 @@
     </row>
     <row r="181" spans="2:10" ht="15" customHeight="1">
       <c r="B181" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C181" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D181" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E181" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F181" s="15">
-        <v>2000</v>
+        <v>30000000</v>
       </c>
       <c r="G181" s="16">
-        <v>9897.50</v>
+        <v>29852.82</v>
       </c>
       <c r="H181" s="17">
-        <v>0.0017367287767</v>
+        <v>0.0059705749732</v>
       </c>
       <c r="I181" s="16">
-        <v>7.88</v>
+        <v>5.62</v>
       </c>
       <c r="J181" s="11" t="s">
         <v>13</v>
@@ -6780,7 +6584,7 @@
     </row>
     <row r="182" spans="2:10" ht="15" customHeight="1">
       <c r="B182" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C182" s="13" t="s">
         <v>264</v>
@@ -6789,19 +6593,19 @@
         <v>13</v>
       </c>
       <c r="E182" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F182" s="15">
-        <v>1500</v>
+        <v>27500000</v>
       </c>
       <c r="G182" s="16">
-        <v>7486.16</v>
+        <v>27388.79</v>
       </c>
       <c r="H182" s="17">
-        <v>0.001313607426</v>
+        <v>0.0054777680675</v>
       </c>
       <c r="I182" s="16">
-        <v>7.50</v>
+        <v>5.70</v>
       </c>
       <c r="J182" s="11" t="s">
         <v>13</v>
@@ -6818,19 +6622,19 @@
         <v>13</v>
       </c>
       <c r="E183" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F183" s="15">
-        <v>1500</v>
+        <v>10000000</v>
       </c>
       <c r="G183" s="16">
-        <v>7485.23</v>
+        <v>9919.16</v>
       </c>
       <c r="H183" s="17">
-        <v>0.0013134442376</v>
+        <v>0.001983835646</v>
       </c>
       <c r="I183" s="16">
-        <v>8</v>
+        <v>5.61</v>
       </c>
       <c r="J183" s="11" t="s">
         <v>13</v>
@@ -6838,28 +6642,28 @@
     </row>
     <row r="184" spans="2:10" ht="15" customHeight="1">
       <c r="B184" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C184" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C184" s="13" t="s">
-        <v>268</v>
-      </c>
       <c r="D184" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E184" s="13" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F184" s="15">
-        <v>1500</v>
+        <v>9000000</v>
       </c>
       <c r="G184" s="16">
-        <v>7474.16</v>
+        <v>8917.72</v>
       </c>
       <c r="H184" s="17">
-        <v>0.0013115017685</v>
+        <v>0.0017835472779</v>
       </c>
       <c r="I184" s="16">
-        <v>7.43</v>
+        <v>5.61</v>
       </c>
       <c r="J184" s="11" t="s">
         <v>13</v>
@@ -6867,28 +6671,28 @@
     </row>
     <row r="185" spans="2:10" ht="15" customHeight="1">
       <c r="B185" s="12" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="C185" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D185" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E185" s="13" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F185" s="15">
-        <v>1500</v>
+        <v>2500000</v>
       </c>
       <c r="G185" s="16">
-        <v>7463.42</v>
+        <v>2495.71</v>
       </c>
       <c r="H185" s="17">
-        <v>0.001309617205</v>
+        <v>0.0004991429173</v>
       </c>
       <c r="I185" s="16">
-        <v>7.46</v>
+        <v>5.70</v>
       </c>
       <c r="J185" s="11" t="s">
         <v>13</v>
@@ -6896,57 +6700,36 @@
     </row>
     <row r="186" spans="2:10" ht="15" customHeight="1">
       <c r="B186" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="C186" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="D186" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E186" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F186" s="15">
-        <v>1500</v>
-      </c>
-      <c r="G186" s="16">
-        <v>7459.34</v>
-      </c>
-      <c r="H186" s="17">
-        <v>0.0013089012815</v>
-      </c>
-      <c r="I186" s="16">
-        <v>7.96</v>
+        <v>13</v>
       </c>
       <c r="J186" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="187" spans="2:10" ht="15" customHeight="1">
-      <c r="B187" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C187" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D187" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E187" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F187" s="15">
-        <v>1500</v>
-      </c>
-      <c r="G187" s="16">
-        <v>7457.46</v>
-      </c>
-      <c r="H187" s="17">
-        <v>0.0013085713951</v>
-      </c>
-      <c r="I187" s="16">
-        <v>7.71</v>
+      <c r="B187" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" s="9">
+        <v>143508.38</v>
+      </c>
+      <c r="H187" s="10">
+        <v>0.0287017287503</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J187" s="11" t="s">
         <v>13</v>
@@ -6954,202 +6737,132 @@
     </row>
     <row r="188" spans="2:10" ht="15" customHeight="1">
       <c r="B188" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C188" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="D188" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E188" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F188" s="15">
-        <v>1500</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C188" s="8"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="8"/>
+      <c r="F188" s="9"/>
       <c r="G188" s="16">
-        <v>7447.96</v>
+        <v>53495.14</v>
       </c>
       <c r="H188" s="17">
-        <v>0.0013069044163</v>
-      </c>
-      <c r="I188" s="16">
-        <v>7.97</v>
-      </c>
-      <c r="J188" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>0.01069904766355333</v>
+      </c>
+      <c r="I188" s="9"/>
+      <c r="J188" s="11"/>
     </row>
     <row r="189" spans="2:10" ht="15" customHeight="1">
       <c r="B189" s="12" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C189" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E189" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F189" s="15">
-        <v>1500</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="D189" s="9"/>
+      <c r="E189" s="8"/>
+      <c r="F189" s="9"/>
       <c r="G189" s="16">
-        <v>7439.79</v>
+        <v>45002.18</v>
       </c>
       <c r="H189" s="17">
-        <v>0.0013054708144</v>
+        <v>0.009000452541741297</v>
       </c>
       <c r="I189" s="16">
-        <v>7.39</v>
-      </c>
-      <c r="J189" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>5.81</v>
+      </c>
+      <c r="J189" s="11"/>
     </row>
     <row r="190" spans="2:10" ht="15" customHeight="1">
       <c r="B190" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C190" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D190" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E190" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F190" s="15">
-        <v>1500</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C190" s="8"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="8"/>
+      <c r="F190" s="9"/>
       <c r="G190" s="16">
-        <v>7439.66</v>
+        <v>20004.34</v>
       </c>
       <c r="H190" s="17">
-        <v>0.0013054480031</v>
-      </c>
-      <c r="I190" s="16">
-        <v>7.79</v>
-      </c>
-      <c r="J190" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>0.004000875353124161</v>
+      </c>
+      <c r="I190" s="9"/>
+      <c r="J190" s="11"/>
     </row>
     <row r="191" spans="2:10" ht="15" customHeight="1">
       <c r="B191" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C191" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="D191" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E191" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F191" s="15">
-        <v>1300</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="D191" s="9"/>
+      <c r="E191" s="8"/>
+      <c r="F191" s="9"/>
       <c r="G191" s="16">
-        <v>6486.54</v>
+        <v>15004.66</v>
       </c>
       <c r="H191" s="17">
-        <v>0.001138202645</v>
+        <v>0.0030009375153595657</v>
       </c>
       <c r="I191" s="16">
-        <v>7.58</v>
-      </c>
-      <c r="J191" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>5.81</v>
+      </c>
+      <c r="J191" s="11"/>
     </row>
     <row r="192" spans="2:10" ht="15" customHeight="1">
       <c r="B192" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="C192" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="D192" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F192" s="15">
-        <v>1200</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C192" s="8"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="8"/>
+      <c r="F192" s="9"/>
       <c r="G192" s="16">
-        <v>5979.47</v>
+        <v>10002.06</v>
       </c>
       <c r="H192" s="17">
-        <v>0.0010492263318</v>
-      </c>
-      <c r="I192" s="16">
-        <v>7.83</v>
-      </c>
-      <c r="J192" s="11" t="s">
-        <v>13</v>
-      </c>
+        <v>0.002000415676521647</v>
+      </c>
+      <c r="I192" s="9"/>
+      <c r="J192" s="11"/>
     </row>
     <row r="193" spans="2:10" ht="15" customHeight="1">
-      <c r="B193" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C193" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D193" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E193" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F193" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G193" s="16">
-        <v>4994.83</v>
-      </c>
-      <c r="H193" s="17">
-        <v>0.0008764501132</v>
-      </c>
-      <c r="I193" s="16">
-        <v>7.56</v>
-      </c>
-      <c r="J193" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="B193" s="7"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="8"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="10"/>
+      <c r="I193" s="9"/>
+      <c r="J193" s="11"/>
     </row>
     <row r="194" spans="2:10" ht="15" customHeight="1">
-      <c r="B194" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="C194" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="D194" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E194" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F194" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G194" s="16">
-        <v>4994.79</v>
-      </c>
-      <c r="H194" s="17">
-        <v>0.0008764430944</v>
-      </c>
-      <c r="I194" s="16">
-        <v>7.63</v>
+      <c r="B194" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="9">
+        <v>13629.33</v>
+      </c>
+      <c r="H194" s="10">
+        <v>0.0027258710098</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J194" s="11" t="s">
         <v>13</v>
@@ -7157,28 +6870,28 @@
     </row>
     <row r="195" spans="2:10" ht="15" customHeight="1">
       <c r="B195" s="12" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C195" s="13" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D195" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E195" s="13" t="s">
-        <v>58</v>
+        <v>280</v>
       </c>
       <c r="F195" s="15">
-        <v>1000</v>
+        <v>121788.821</v>
       </c>
       <c r="G195" s="16">
-        <v>4983.73</v>
+        <v>13629.33</v>
       </c>
       <c r="H195" s="17">
-        <v>0.00087450238</v>
-      </c>
-      <c r="I195" s="16">
-        <v>7.45</v>
+        <v>0.0027258710098</v>
+      </c>
+      <c r="I195" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="J195" s="11" t="s">
         <v>13</v>
@@ -7186,57 +6899,36 @@
     </row>
     <row r="196" spans="2:10" ht="15" customHeight="1">
       <c r="B196" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C196" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="D196" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E196" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F196" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G196" s="16">
-        <v>4980.69</v>
-      </c>
-      <c r="H196" s="17">
-        <v>0.0008739689468</v>
-      </c>
-      <c r="I196" s="16">
-        <v>7.45</v>
+        <v>13</v>
       </c>
       <c r="J196" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="197" spans="2:10" ht="15" customHeight="1">
-      <c r="B197" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C197" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="D197" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E197" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F197" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G197" s="16">
-        <v>4976.64</v>
-      </c>
-      <c r="H197" s="17">
-        <v>0.0008732582874</v>
-      </c>
-      <c r="I197" s="16">
-        <v>7.45</v>
+      <c r="B197" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G197" s="9">
+        <v>59434.50</v>
+      </c>
+      <c r="H197" s="10">
+        <v>0.0118869218468</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J197" s="11" t="s">
         <v>13</v>
@@ -7244,1066 +6936,158 @@
     </row>
     <row r="198" spans="2:10" ht="15" customHeight="1">
       <c r="B198" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J198" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" ht="15" customHeight="1">
+      <c r="B199" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C199" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D199" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F199" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G199" s="19">
+        <v>-570679.8594530486</v>
+      </c>
+      <c r="H199" s="20">
+        <v>-0.11413618166042623</v>
+      </c>
+      <c r="I199" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J199" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" ht="15" customHeight="1">
+      <c r="B200" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C200" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D200" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E200" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F200" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G200" s="19">
+        <v>4999990.81054695</v>
+      </c>
+      <c r="H200" s="20">
+        <v>0.999999999991873</v>
+      </c>
+      <c r="I200" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J200" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" ht="15" customHeight="1">
+      <c r="B203" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C203" s="22"/>
+      <c r="D203" s="22"/>
+      <c r="E203" s="22"/>
+      <c r="F203" s="22"/>
+      <c r="G203" s="22"/>
+      <c r="H203" s="22"/>
+      <c r="I203" s="22"/>
+    </row>
+    <row r="204" spans="2:8" ht="15" customHeight="1">
+      <c r="B204" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C204" s="22"/>
+      <c r="D204" s="22"/>
+      <c r="E204" s="22"/>
+      <c r="F204" s="22"/>
+      <c r="G204" s="22"/>
+      <c r="H204" s="22"/>
+    </row>
+    <row r="205" spans="2:8" ht="15" customHeight="1">
+      <c r="B205" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C198" s="13" t="s">
+      <c r="C205" s="22"/>
+      <c r="D205" s="22"/>
+      <c r="E205" s="22"/>
+      <c r="F205" s="22"/>
+      <c r="G205" s="22"/>
+      <c r="H205" s="22"/>
+    </row>
+    <row r="206" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B206" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E198" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F198" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G198" s="16">
-        <v>4972.66</v>
-      </c>
-      <c r="H198" s="17">
-        <v>0.000872559911</v>
-      </c>
-      <c r="I198" s="16">
-        <v>7.72</v>
-      </c>
-      <c r="J198" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="199" spans="2:10" ht="15" customHeight="1">
-      <c r="B199" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C199" s="13" t="s">
+      <c r="C206" s="22"/>
+      <c r="D206" s="22"/>
+      <c r="E206" s="22"/>
+      <c r="F206" s="22"/>
+      <c r="G206" s="22"/>
+      <c r="H206" s="22"/>
+    </row>
+    <row r="207" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B207" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E199" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F199" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G199" s="16">
-        <v>4969.09</v>
-      </c>
-      <c r="H199" s="17">
-        <v>0.0008719334778</v>
-      </c>
-      <c r="I199" s="16">
-        <v>7.33</v>
-      </c>
-      <c r="J199" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="200" spans="2:10" ht="15" customHeight="1">
-      <c r="B200" s="12" t="s">
+      <c r="C207" s="22"/>
+      <c r="D207" s="22"/>
+      <c r="E207" s="22"/>
+      <c r="F207" s="22"/>
+      <c r="G207" s="22"/>
+      <c r="H207" s="22"/>
+    </row>
+    <row r="208" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B208" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="C200" s="13" t="s">
+      <c r="C208" s="22"/>
+      <c r="D208" s="22"/>
+      <c r="E208" s="22"/>
+      <c r="F208" s="22"/>
+      <c r="G208" s="22"/>
+      <c r="H208" s="22"/>
+    </row>
+    <row r="211" ht="15">
+      <c r="B211" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="D200" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E200" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F200" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G200" s="16">
-        <v>4960.13</v>
-      </c>
-      <c r="H200" s="17">
-        <v>0.0008703612536</v>
-      </c>
-      <c r="I200" s="16">
-        <v>7.93</v>
-      </c>
-      <c r="J200" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="201" spans="2:10" ht="15" customHeight="1">
-      <c r="B201" s="12" t="s">
+    </row>
+    <row r="226" ht="15">
+      <c r="B226" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="C201" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="D201" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E201" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F201" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G201" s="16">
-        <v>4958.49</v>
-      </c>
-      <c r="H201" s="17">
-        <v>0.0008700734804</v>
-      </c>
-      <c r="I201" s="16">
-        <v>7.64</v>
-      </c>
-      <c r="J201" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="202" spans="2:10" ht="15" customHeight="1">
-      <c r="B202" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C202" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="D202" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E202" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F202" s="15">
-        <v>800</v>
-      </c>
-      <c r="G202" s="16">
-        <v>3978.06</v>
-      </c>
-      <c r="H202" s="17">
-        <v>0.0006980359967</v>
-      </c>
-      <c r="I202" s="16">
-        <v>7.46</v>
-      </c>
-      <c r="J202" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="203" spans="2:10" ht="15" customHeight="1">
-      <c r="B203" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="C203" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="D203" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E203" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F203" s="15">
-        <v>500</v>
-      </c>
-      <c r="G203" s="16">
-        <v>2491.05</v>
-      </c>
-      <c r="H203" s="17">
-        <v>0.0004371081807</v>
-      </c>
-      <c r="I203" s="16">
-        <v>7.71</v>
-      </c>
-      <c r="J203" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="204" spans="2:10" ht="15" customHeight="1">
-      <c r="B204" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="C204" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="D204" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E204" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F204" s="15">
-        <v>500</v>
-      </c>
-      <c r="G204" s="16">
-        <v>2490.71</v>
-      </c>
-      <c r="H204" s="17">
-        <v>0.0004370485205</v>
-      </c>
-      <c r="I204" s="16">
-        <v>8.01</v>
-      </c>
-      <c r="J204" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="205" spans="2:10" ht="15" customHeight="1">
-      <c r="B205" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C205" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="D205" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E205" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F205" s="15">
-        <v>500</v>
-      </c>
-      <c r="G205" s="16">
-        <v>2483.19</v>
-      </c>
-      <c r="H205" s="17">
-        <v>0.0004357289751</v>
-      </c>
-      <c r="I205" s="16">
-        <v>7.97</v>
-      </c>
-      <c r="J205" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="206" spans="2:10" ht="15" customHeight="1">
-      <c r="B206" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C206" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="D206" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E206" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F206" s="15">
-        <v>500</v>
-      </c>
-      <c r="G206" s="16">
-        <v>2480.55</v>
-      </c>
-      <c r="H206" s="17">
-        <v>0.0004352657304</v>
-      </c>
-      <c r="I206" s="16">
-        <v>7.34</v>
-      </c>
-      <c r="J206" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="207" spans="2:10" ht="15" customHeight="1">
-      <c r="B207" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C207" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="D207" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E207" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F207" s="15">
-        <v>500</v>
-      </c>
-      <c r="G207" s="16">
-        <v>2479.90</v>
-      </c>
-      <c r="H207" s="17">
-        <v>0.000435151674</v>
-      </c>
-      <c r="I207" s="16">
-        <v>7.59</v>
-      </c>
-      <c r="J207" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="208" spans="2:10" ht="15" customHeight="1">
-      <c r="B208" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J208" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="209" spans="2:10" ht="15" customHeight="1">
-      <c r="B209" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C209" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D209" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E209" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F209" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I209" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J209" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="210" spans="2:10" ht="15" customHeight="1">
-      <c r="B210" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J210" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="211" spans="2:10" ht="15" customHeight="1">
-      <c r="B211" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D211" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E211" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F211" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G211" s="9">
-        <v>620496.82</v>
-      </c>
-      <c r="H211" s="10">
-        <v>0.10887948302089999</v>
-      </c>
-      <c r="I211" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J211" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="212" spans="2:10" ht="15" customHeight="1">
-      <c r="B212" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C212" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="D212" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E212" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F212" s="15">
-        <v>180000000</v>
-      </c>
-      <c r="G212" s="16">
-        <v>177621.30</v>
-      </c>
-      <c r="H212" s="17">
-        <v>0.031167468864</v>
-      </c>
-      <c r="I212" s="16">
-        <v>6.52</v>
-      </c>
-      <c r="J212" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="213" spans="2:10" ht="15" customHeight="1">
-      <c r="B213" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C213" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D213" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E213" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F213" s="15">
-        <v>132576600</v>
-      </c>
-      <c r="G213" s="16">
-        <v>130664.58</v>
-      </c>
-      <c r="H213" s="17">
-        <v>0.0229279046419</v>
-      </c>
-      <c r="I213" s="16">
-        <v>6.51</v>
-      </c>
-      <c r="J213" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="214" spans="2:10" ht="15" customHeight="1">
-      <c r="B214" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C214" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="D214" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E214" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F214" s="15">
-        <v>100000000</v>
-      </c>
-      <c r="G214" s="16">
-        <v>98436.30</v>
-      </c>
-      <c r="H214" s="17">
-        <v>0.0172727612923</v>
-      </c>
-      <c r="I214" s="16">
-        <v>6.52</v>
-      </c>
-      <c r="J214" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="215" spans="2:10" ht="15" customHeight="1">
-      <c r="B215" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C215" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="D215" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E215" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F215" s="15">
-        <v>75000000</v>
-      </c>
-      <c r="G215" s="16">
-        <v>74658.30</v>
-      </c>
-      <c r="H215" s="17">
-        <v>0.013100400913</v>
-      </c>
-      <c r="I215" s="16">
-        <v>6.43</v>
-      </c>
-      <c r="J215" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="216" spans="2:10" ht="15" customHeight="1">
-      <c r="B216" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C216" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D216" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E216" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F216" s="15">
-        <v>50000000</v>
-      </c>
-      <c r="G216" s="16">
-        <v>49824.60</v>
-      </c>
-      <c r="H216" s="17">
-        <v>0.0087427953131</v>
-      </c>
-      <c r="I216" s="16">
-        <v>6.43</v>
-      </c>
-      <c r="J216" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="217" spans="2:10" ht="15" customHeight="1">
-      <c r="B217" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C217" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D217" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E217" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F217" s="15">
-        <v>50000000</v>
-      </c>
-      <c r="G217" s="16">
-        <v>49399.80</v>
-      </c>
-      <c r="H217" s="17">
-        <v>0.0086682550369</v>
-      </c>
-      <c r="I217" s="16">
-        <v>6.52</v>
-      </c>
-      <c r="J217" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="218" spans="2:10" ht="15" customHeight="1">
-      <c r="B218" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C218" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="D218" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E218" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F218" s="15">
-        <v>25000000</v>
-      </c>
-      <c r="G218" s="16">
-        <v>24978.23</v>
-      </c>
-      <c r="H218" s="17">
-        <v>0.0043829664899</v>
-      </c>
-      <c r="I218" s="16">
-        <v>6.37</v>
-      </c>
-      <c r="J218" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="219" spans="2:10" ht="15" customHeight="1">
-      <c r="B219" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="C219" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="D219" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E219" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F219" s="15">
-        <v>15000000</v>
-      </c>
-      <c r="G219" s="16">
-        <v>14913.71</v>
-      </c>
-      <c r="H219" s="17">
-        <v>0.0026169304698</v>
-      </c>
-      <c r="I219" s="16">
-        <v>6.40</v>
-      </c>
-      <c r="J219" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="220" spans="2:10" ht="15" customHeight="1">
-      <c r="B220" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J220" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="221" spans="2:10" ht="15" customHeight="1">
-      <c r="B221" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C221" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D221" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E221" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F221" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G221" s="9">
-        <v>253502.25</v>
-      </c>
-      <c r="H221" s="10">
-        <v>0.0444824099574</v>
-      </c>
-      <c r="I221" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J221" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="222" spans="2:10" ht="15" customHeight="1">
-      <c r="B222" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="C222" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="D222" s="9"/>
-      <c r="E222" s="8"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="14">
-        <v>50531.09</v>
-      </c>
-      <c r="H222" s="17">
-        <v>0.008866764144989938</v>
-      </c>
-      <c r="I222" s="14">
-        <v>6.71</v>
-      </c>
-      <c r="J222" s="11"/>
-    </row>
-    <row r="223" spans="2:10" ht="15" customHeight="1">
-      <c r="B223" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="C223" s="8"/>
-      <c r="D223" s="9"/>
-      <c r="E223" s="8"/>
-      <c r="F223" s="9"/>
-      <c r="G223" s="14">
-        <v>43899.95</v>
-      </c>
-      <c r="H223" s="17">
-        <v>0.007703188326767759</v>
-      </c>
-      <c r="I223" s="9"/>
-      <c r="J223" s="11"/>
-    </row>
-    <row r="224" spans="2:10" ht="15" customHeight="1">
-      <c r="B224" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="C224" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="D224" s="9"/>
-      <c r="E224" s="8"/>
-      <c r="F224" s="9"/>
-      <c r="G224" s="14">
-        <v>42624.03</v>
-      </c>
-      <c r="H224" s="17">
-        <v>0.00747930078134027</v>
-      </c>
-      <c r="I224" s="14">
-        <v>6.60</v>
-      </c>
-      <c r="J224" s="11"/>
-    </row>
-    <row r="225" spans="2:10" ht="15" customHeight="1">
-      <c r="B225" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="C225" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="D225" s="9"/>
-      <c r="E225" s="8"/>
-      <c r="F225" s="9"/>
-      <c r="G225" s="14">
-        <v>40825.03</v>
-      </c>
-      <c r="H225" s="17">
-        <v>0.007163627624540429</v>
-      </c>
-      <c r="I225" s="14">
-        <v>6.60</v>
-      </c>
-      <c r="J225" s="11"/>
-    </row>
-    <row r="226" spans="2:10" ht="15" customHeight="1">
-      <c r="B226" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="C226" s="8"/>
-      <c r="D226" s="9"/>
-      <c r="E226" s="8"/>
-      <c r="F226" s="9"/>
-      <c r="G226" s="14">
-        <v>36312.37</v>
-      </c>
-      <c r="H226" s="17">
-        <v>0.006371784585205036</v>
-      </c>
-      <c r="I226" s="9"/>
-      <c r="J226" s="11"/>
-    </row>
-    <row r="227" spans="2:10" ht="15" customHeight="1">
-      <c r="B227" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="C227" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="D227" s="9"/>
-      <c r="E227" s="8"/>
-      <c r="F227" s="9"/>
-      <c r="G227" s="14">
-        <v>21992.93</v>
-      </c>
-      <c r="H227" s="17">
-        <v>0.0038591315399543837</v>
-      </c>
-      <c r="I227" s="14">
-        <v>6.71</v>
-      </c>
-      <c r="J227" s="11"/>
-    </row>
-    <row r="228" spans="2:10" ht="15" customHeight="1">
-      <c r="B228" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="C228" s="8"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="8"/>
-      <c r="F228" s="9"/>
-      <c r="G228" s="14">
-        <v>9316.17</v>
-      </c>
-      <c r="H228" s="17">
-        <v>0.0016347219528537959</v>
-      </c>
-      <c r="I228" s="9"/>
-      <c r="J228" s="11"/>
-    </row>
-    <row r="229" spans="2:10" ht="15" customHeight="1">
-      <c r="B229" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="C229" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="D229" s="9"/>
-      <c r="E229" s="8"/>
-      <c r="F229" s="9"/>
-      <c r="G229" s="14">
-        <v>8000.68</v>
-      </c>
-      <c r="H229" s="17">
-        <v>0.0014038910017483911</v>
-      </c>
-      <c r="I229" s="14">
-        <v>6.60</v>
-      </c>
-      <c r="J229" s="11"/>
-    </row>
-    <row r="230" spans="2:10" ht="15" customHeight="1">
-      <c r="B230" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J230" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="231" spans="2:10" ht="15" customHeight="1">
-      <c r="B231" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C231" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E231" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F231" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G231" s="9">
-        <v>13287.88</v>
-      </c>
-      <c r="H231" s="10">
-        <v>0.0023316437058</v>
-      </c>
-      <c r="I231" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J231" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="232" spans="2:10" ht="15" customHeight="1">
-      <c r="B232" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="C232" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="D232" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E232" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="F232" s="15">
-        <v>121788.821</v>
-      </c>
-      <c r="G232" s="16">
-        <v>13287.88</v>
-      </c>
-      <c r="H232" s="17">
-        <v>0.0023316437058</v>
-      </c>
-      <c r="I232" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J232" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="233" spans="2:10" ht="15" customHeight="1">
-      <c r="B233" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J233" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="234" spans="2:10" ht="15" customHeight="1">
-      <c r="B234" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E234" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F234" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G234" s="9">
-        <v>179748.91</v>
-      </c>
-      <c r="H234" s="10">
-        <v>0.0315408036973</v>
-      </c>
-      <c r="I234" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J234" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="235" spans="2:10" ht="15" customHeight="1">
-      <c r="B235" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J235" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="236" spans="2:10" ht="15" customHeight="1">
-      <c r="B236" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="C236" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D236" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E236" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F236" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G236" s="19">
-        <v>18169.02982670907</v>
-      </c>
-      <c r="H236" s="20">
-        <v>0.0031881461931313262</v>
-      </c>
-      <c r="I236" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J236" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="237" spans="2:10" ht="15" customHeight="1">
-      <c r="B237" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="C237" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D237" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E237" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F237" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G237" s="19">
-        <v>5698932.45982671</v>
-      </c>
-      <c r="H237" s="20">
-        <v>0.9999999999895312</v>
-      </c>
-      <c r="I237" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J237" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="240" spans="2:9" ht="15" customHeight="1">
-      <c r="B240" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="C240" s="22"/>
-      <c r="D240" s="22"/>
-      <c r="E240" s="22"/>
-      <c r="F240" s="22"/>
-      <c r="G240" s="22"/>
-      <c r="H240" s="22"/>
-      <c r="I240" s="22"/>
-    </row>
-    <row r="241" spans="2:8" ht="15" customHeight="1">
-      <c r="B241" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="C241" s="22"/>
-      <c r="D241" s="22"/>
-      <c r="E241" s="22"/>
-      <c r="F241" s="22"/>
-      <c r="G241" s="22"/>
-      <c r="H241" s="22"/>
-    </row>
-    <row r="242" spans="2:8" ht="15" customHeight="1">
-      <c r="B242" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="C242" s="22"/>
-      <c r="D242" s="22"/>
-      <c r="E242" s="22"/>
-      <c r="F242" s="22"/>
-      <c r="G242" s="22"/>
-      <c r="H242" s="22"/>
-    </row>
-    <row r="243" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B243" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="C243" s="22"/>
-      <c r="D243" s="22"/>
-      <c r="E243" s="22"/>
-      <c r="F243" s="22"/>
-      <c r="G243" s="22"/>
-      <c r="H243" s="22"/>
-    </row>
-    <row r="244" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B244" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="C244" s="22"/>
-      <c r="D244" s="22"/>
-      <c r="E244" s="22"/>
-      <c r="F244" s="22"/>
-      <c r="G244" s="22"/>
-      <c r="H244" s="22"/>
-    </row>
-    <row r="245" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B245" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="C245" s="22"/>
-      <c r="D245" s="22"/>
-      <c r="E245" s="22"/>
-      <c r="F245" s="22"/>
-      <c r="G245" s="22"/>
-      <c r="H245" s="22"/>
-    </row>
-    <row r="246" spans="2:7" ht="52.5" customHeight="1">
-      <c r="B246" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="C246" s="24"/>
-      <c r="D246" s="24"/>
-      <c r="E246" s="24"/>
-      <c r="F246" s="24"/>
-      <c r="G246" s="24"/>
-    </row>
-    <row r="249" ht="15">
-      <c r="B249" s="22" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="264" ht="15">
-      <c r="B264" s="22" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="265" ht="15">
-      <c r="B265" s="22" t="s">
-        <v>341</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B242:H242"/>
-    <mergeCell ref="B243:H243"/>
-    <mergeCell ref="B244:H244"/>
-    <mergeCell ref="B245:H245"/>
-    <mergeCell ref="B246:G246"/>
+  <mergeCells count="9">
+    <mergeCell ref="B205:H205"/>
+    <mergeCell ref="B206:H206"/>
+    <mergeCell ref="B207:H207"/>
+    <mergeCell ref="B208:H208"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B240:I240"/>
-    <mergeCell ref="B241:H241"/>
+    <mergeCell ref="B203:I203"/>
+    <mergeCell ref="B204:H204"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
